--- a/sourcedata/Fact_SalesTarget.xlsx
+++ b/sourcedata/Fact_SalesTarget.xlsx
@@ -574,31 +574,31 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>304</v>
+        <v>238</v>
       </c>
       <c r="J2" t="n">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="K2" t="n">
-        <v>306</v>
+        <v>246</v>
       </c>
       <c r="L2" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="M2" t="n">
-        <v>100.7</v>
+        <v>103.4</v>
       </c>
       <c r="N2" t="n">
-        <v>93.2</v>
+        <v>103.8</v>
       </c>
       <c r="O2" t="n">
-        <v>40128</v>
+        <v>35700</v>
       </c>
       <c r="P2" t="n">
-        <v>40392</v>
+        <v>36900</v>
       </c>
       <c r="Q2" t="n">
-        <v>100.7</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="3">
@@ -639,31 +639,31 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="J3" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="K3" t="n">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M3" t="n">
-        <v>104.6</v>
+        <v>102.4</v>
       </c>
       <c r="N3" t="n">
-        <v>84.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="O3" t="n">
-        <v>50142</v>
+        <v>42714</v>
       </c>
       <c r="P3" t="n">
-        <v>52471</v>
+        <v>43722</v>
       </c>
       <c r="Q3" t="n">
-        <v>104.6</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="4">
@@ -704,31 +704,31 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="J4" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K4" t="n">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="L4" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M4" t="n">
-        <v>89</v>
+        <v>99.2</v>
       </c>
       <c r="N4" t="n">
-        <v>98.2</v>
+        <v>110</v>
       </c>
       <c r="O4" t="n">
-        <v>15500</v>
+        <v>19987</v>
       </c>
       <c r="P4" t="n">
-        <v>13800</v>
+        <v>19829</v>
       </c>
       <c r="Q4" t="n">
-        <v>89</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="5">
@@ -769,31 +769,31 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>420</v>
+        <v>288</v>
       </c>
       <c r="J5" t="n">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
-        <v>465</v>
+        <v>277</v>
       </c>
       <c r="L5" t="n">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>110.7</v>
+        <v>96.2</v>
       </c>
       <c r="N5" t="n">
-        <v>113.9</v>
+        <v>104.9</v>
       </c>
       <c r="O5" t="n">
-        <v>60900</v>
+        <v>32256</v>
       </c>
       <c r="P5" t="n">
-        <v>67425</v>
+        <v>31024</v>
       </c>
       <c r="Q5" t="n">
-        <v>110.7</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="6">
@@ -834,31 +834,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>417</v>
+        <v>434</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="K6" t="n">
-        <v>431</v>
+        <v>385</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>103.4</v>
+        <v>88.7</v>
       </c>
       <c r="N6" t="n">
-        <v>93.5</v>
+        <v>86.2</v>
       </c>
       <c r="O6" t="n">
-        <v>55878</v>
+        <v>37324</v>
       </c>
       <c r="P6" t="n">
-        <v>57754</v>
+        <v>33110</v>
       </c>
       <c r="Q6" t="n">
-        <v>103.4</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="7">
@@ -899,31 +899,31 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>272</v>
+        <v>421</v>
       </c>
       <c r="J7" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="K7" t="n">
-        <v>295</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>108.5</v>
+        <v>102.1</v>
       </c>
       <c r="N7" t="n">
-        <v>109.4</v>
+        <v>102.2</v>
       </c>
       <c r="O7" t="n">
-        <v>26384</v>
+        <v>26523</v>
       </c>
       <c r="P7" t="n">
-        <v>28615</v>
+        <v>27090</v>
       </c>
       <c r="Q7" t="n">
-        <v>108.5</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="8">
@@ -964,31 +964,31 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>310</v>
+        <v>177</v>
       </c>
       <c r="J8" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="K8" t="n">
-        <v>329</v>
+        <v>191</v>
       </c>
       <c r="L8" t="n">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="M8" t="n">
-        <v>106.1</v>
+        <v>107.9</v>
       </c>
       <c r="N8" t="n">
-        <v>95</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>38440</v>
+        <v>22302</v>
       </c>
       <c r="P8" t="n">
-        <v>40796</v>
+        <v>24066</v>
       </c>
       <c r="Q8" t="n">
-        <v>106.1</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="9">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="J9" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K9" t="n">
-        <v>254</v>
+        <v>302</v>
       </c>
       <c r="L9" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="M9" t="n">
-        <v>110.4</v>
+        <v>111.9</v>
       </c>
       <c r="N9" t="n">
-        <v>86.7</v>
+        <v>91.7</v>
       </c>
       <c r="O9" t="n">
-        <v>17940</v>
+        <v>27000</v>
       </c>
       <c r="P9" t="n">
-        <v>19812</v>
+        <v>30200</v>
       </c>
       <c r="Q9" t="n">
-        <v>110.4</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="10">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>436</v>
+        <v>199</v>
       </c>
       <c r="J10" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="K10" t="n">
-        <v>429</v>
+        <v>217</v>
       </c>
       <c r="L10" t="n">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>98.40000000000001</v>
+        <v>109</v>
       </c>
       <c r="N10" t="n">
-        <v>105.2</v>
+        <v>107.5</v>
       </c>
       <c r="O10" t="n">
-        <v>31828</v>
+        <v>12139</v>
       </c>
       <c r="P10" t="n">
-        <v>31317</v>
+        <v>13237</v>
       </c>
       <c r="Q10" t="n">
-        <v>98.40000000000001</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -1159,31 +1159,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="J11" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K11" t="n">
-        <v>393</v>
+        <v>348</v>
       </c>
       <c r="L11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M11" t="n">
-        <v>95.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>104.3</v>
+        <v>112.7</v>
       </c>
       <c r="O11" t="n">
-        <v>43870</v>
+        <v>56823</v>
       </c>
       <c r="P11" t="n">
-        <v>42051</v>
+        <v>49068</v>
       </c>
       <c r="Q11" t="n">
-        <v>95.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1224,31 +1224,31 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>551</v>
+        <v>343</v>
       </c>
       <c r="J12" t="n">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="K12" t="n">
-        <v>551</v>
+        <v>308</v>
       </c>
       <c r="L12" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="M12" t="n">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="N12" t="n">
-        <v>89.3</v>
+        <v>106.5</v>
       </c>
       <c r="O12" t="n">
-        <v>77140</v>
+        <v>51107</v>
       </c>
       <c r="P12" t="n">
-        <v>77140</v>
+        <v>45892</v>
       </c>
       <c r="Q12" t="n">
-        <v>100</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="13">
@@ -1289,31 +1289,31 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>425</v>
+        <v>322</v>
       </c>
       <c r="J13" t="n">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="K13" t="n">
-        <v>474</v>
+        <v>301</v>
       </c>
       <c r="L13" t="n">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="M13" t="n">
-        <v>111.5</v>
+        <v>93.5</v>
       </c>
       <c r="N13" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="O13" t="n">
-        <v>56525</v>
+        <v>35098</v>
       </c>
       <c r="P13" t="n">
-        <v>63042</v>
+        <v>32809</v>
       </c>
       <c r="Q13" t="n">
-        <v>111.5</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="14">
@@ -1354,31 +1354,31 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>369</v>
+        <v>163</v>
       </c>
       <c r="J14" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>333</v>
+        <v>159</v>
       </c>
       <c r="L14" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="M14" t="n">
-        <v>90.2</v>
+        <v>97.5</v>
       </c>
       <c r="N14" t="n">
-        <v>115.1</v>
+        <v>100</v>
       </c>
       <c r="O14" t="n">
-        <v>53874</v>
+        <v>13692</v>
       </c>
       <c r="P14" t="n">
-        <v>48618</v>
+        <v>13356</v>
       </c>
       <c r="Q14" t="n">
-        <v>90.2</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15">
@@ -1419,31 +1419,31 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>283</v>
+        <v>171</v>
       </c>
       <c r="J15" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K15" t="n">
-        <v>293</v>
+        <v>165</v>
       </c>
       <c r="L15" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M15" t="n">
-        <v>103.5</v>
+        <v>96.5</v>
       </c>
       <c r="N15" t="n">
-        <v>102.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>18961</v>
+        <v>13851</v>
       </c>
       <c r="P15" t="n">
-        <v>19631</v>
+        <v>13365</v>
       </c>
       <c r="Q15" t="n">
-        <v>103.5</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="16">
@@ -1484,31 +1484,31 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>472</v>
+        <v>147</v>
       </c>
       <c r="J16" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="K16" t="n">
-        <v>417</v>
+        <v>138</v>
       </c>
       <c r="L16" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="M16" t="n">
-        <v>88.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>87.8</v>
+        <v>100</v>
       </c>
       <c r="O16" t="n">
-        <v>42008</v>
+        <v>20727</v>
       </c>
       <c r="P16" t="n">
-        <v>37113</v>
+        <v>19458</v>
       </c>
       <c r="Q16" t="n">
-        <v>88.3</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1549,31 +1549,31 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>332</v>
+        <v>153</v>
       </c>
       <c r="J17" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="M17" t="n">
-        <v>112</v>
+        <v>92.8</v>
       </c>
       <c r="N17" t="n">
-        <v>101.6</v>
+        <v>96</v>
       </c>
       <c r="O17" t="n">
-        <v>46148</v>
+        <v>10863</v>
       </c>
       <c r="P17" t="n">
-        <v>51708</v>
+        <v>10082</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="18">
@@ -1614,31 +1614,31 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>437</v>
+        <v>302</v>
       </c>
       <c r="J18" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K18" t="n">
-        <v>394</v>
+        <v>324</v>
       </c>
       <c r="L18" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M18" t="n">
-        <v>90.2</v>
+        <v>107.3</v>
       </c>
       <c r="N18" t="n">
-        <v>105.4</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>63802</v>
+        <v>21442</v>
       </c>
       <c r="P18" t="n">
-        <v>57524</v>
+        <v>23004</v>
       </c>
       <c r="Q18" t="n">
-        <v>90.2</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="19">
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>390</v>
+        <v>328</v>
       </c>
       <c r="J19" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="K19" t="n">
-        <v>432</v>
+        <v>303</v>
       </c>
       <c r="L19" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="M19" t="n">
-        <v>110.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>97.09999999999999</v>
+        <v>102.4</v>
       </c>
       <c r="O19" t="n">
-        <v>41340</v>
+        <v>46248</v>
       </c>
       <c r="P19" t="n">
-        <v>45792</v>
+        <v>42723</v>
       </c>
       <c r="Q19" t="n">
-        <v>110.8</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1744,31 +1744,31 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>497</v>
+        <v>228</v>
       </c>
       <c r="J20" t="n">
-        <v>102</v>
+        <v>25</v>
       </c>
       <c r="K20" t="n">
-        <v>445</v>
+        <v>201</v>
       </c>
       <c r="L20" t="n">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="M20" t="n">
-        <v>89.5</v>
+        <v>88.2</v>
       </c>
       <c r="N20" t="n">
-        <v>90.2</v>
+        <v>112</v>
       </c>
       <c r="O20" t="n">
-        <v>42245</v>
+        <v>14592</v>
       </c>
       <c r="P20" t="n">
-        <v>37825</v>
+        <v>12864</v>
       </c>
       <c r="Q20" t="n">
-        <v>89.5</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="21">
@@ -1809,31 +1809,31 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>373</v>
+        <v>279</v>
       </c>
       <c r="J21" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="K21" t="n">
-        <v>345</v>
+        <v>238</v>
       </c>
       <c r="L21" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>92.5</v>
+        <v>85.3</v>
       </c>
       <c r="N21" t="n">
-        <v>85.5</v>
+        <v>102.4</v>
       </c>
       <c r="O21" t="n">
-        <v>37673</v>
+        <v>27063</v>
       </c>
       <c r="P21" t="n">
-        <v>34845</v>
+        <v>23086</v>
       </c>
       <c r="Q21" t="n">
-        <v>92.5</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="22">
@@ -1874,31 +1874,31 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>358</v>
+        <v>388</v>
       </c>
       <c r="J22" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="M22" t="n">
-        <v>88.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>105.1</v>
+        <v>100</v>
       </c>
       <c r="O22" t="n">
-        <v>41170</v>
+        <v>22116</v>
       </c>
       <c r="P22" t="n">
-        <v>36570</v>
+        <v>20805</v>
       </c>
       <c r="Q22" t="n">
-        <v>88.8</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1939,31 +1939,31 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>409</v>
+        <v>344</v>
       </c>
       <c r="J23" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="K23" t="n">
-        <v>392</v>
+        <v>351</v>
       </c>
       <c r="L23" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="M23" t="n">
-        <v>95.8</v>
+        <v>102</v>
       </c>
       <c r="N23" t="n">
-        <v>110.1</v>
+        <v>111.7</v>
       </c>
       <c r="O23" t="n">
-        <v>57669</v>
+        <v>45064</v>
       </c>
       <c r="P23" t="n">
-        <v>55272</v>
+        <v>45981</v>
       </c>
       <c r="Q23" t="n">
-        <v>95.8</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
@@ -2004,31 +2004,31 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="J24" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="L24" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M24" t="n">
-        <v>95.40000000000001</v>
+        <v>111.9</v>
       </c>
       <c r="N24" t="n">
-        <v>86.3</v>
+        <v>104.2</v>
       </c>
       <c r="O24" t="n">
-        <v>22923</v>
+        <v>10736</v>
       </c>
       <c r="P24" t="n">
-        <v>21870</v>
+        <v>12017</v>
       </c>
       <c r="Q24" t="n">
-        <v>95.40000000000001</v>
+        <v>111.9</v>
       </c>
     </row>
     <row r="25">
@@ -2069,31 +2069,31 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>407</v>
+        <v>195</v>
       </c>
       <c r="J25" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="K25" t="n">
-        <v>394</v>
+        <v>204</v>
       </c>
       <c r="L25" t="n">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="M25" t="n">
-        <v>96.8</v>
+        <v>104.6</v>
       </c>
       <c r="N25" t="n">
-        <v>104.5</v>
+        <v>100</v>
       </c>
       <c r="O25" t="n">
-        <v>57387</v>
+        <v>16380</v>
       </c>
       <c r="P25" t="n">
-        <v>55554</v>
+        <v>17136</v>
       </c>
       <c r="Q25" t="n">
-        <v>96.8</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="26">
@@ -2134,31 +2134,31 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>90.7</v>
       </c>
       <c r="O26" t="n">
-        <v>750</v>
+        <v>22663</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>22270</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="27">
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>106.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>540</v>
+        <v>16632</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>17688</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="28">
@@ -2264,31 +2264,31 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>1270</v>
+        <v>52200</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>51620</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2329,31 +2329,31 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>282</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>105.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1020</v>
+        <v>30738</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>27141</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="30">
@@ -2394,31 +2394,31 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>301</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>109.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>970</v>
+        <v>41839</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>45731</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>109.3</v>
       </c>
     </row>
     <row r="31">
@@ -2459,31 +2459,31 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>10</v>
+        <v>223</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>89.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1120</v>
+        <v>16725</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>14925</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="32">
@@ -2524,31 +2524,31 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>345</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>361</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>104.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>1350</v>
+        <v>43815</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>45847</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="33">
@@ -2589,31 +2589,31 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>352</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>106.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>103.1</v>
       </c>
       <c r="O33" t="n">
-        <v>560</v>
+        <v>39424</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="34">
@@ -2654,31 +2654,31 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>331</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1170</v>
+        <v>24494</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>23754</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="35">
@@ -2719,31 +2719,31 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>109.5</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>107.7</v>
       </c>
       <c r="O35" t="n">
-        <v>1020</v>
+        <v>8820</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>9660</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="36">
@@ -2784,31 +2784,31 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>87.7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>113.2</v>
       </c>
       <c r="O36" t="n">
-        <v>990</v>
+        <v>22500</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>19725</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="37">
@@ -2849,31 +2849,31 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>340</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>105.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>93.5</v>
       </c>
       <c r="O37" t="n">
-        <v>1080</v>
+        <v>42840</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>45108</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="38">
@@ -2914,31 +2914,31 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>331</v>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38" t="n">
-        <v>1020</v>
+        <v>17874</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>15228</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="39">
@@ -2979,31 +2979,31 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10</v>
+        <v>236</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>97.2</v>
       </c>
       <c r="O39" t="n">
-        <v>980</v>
+        <v>16992</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>16488</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40">
@@ -3044,31 +3044,31 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>1260</v>
+        <v>19190</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>17100</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3109,31 +3109,31 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10</v>
+        <v>139</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41" t="n">
-        <v>1440</v>
+        <v>15290</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>13750</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -3174,31 +3174,31 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>10</v>
+        <v>209</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>106.7</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>104.2</v>
       </c>
       <c r="O42" t="n">
-        <v>1200</v>
+        <v>25289</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>26983</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>106.7</v>
       </c>
     </row>
     <row r="43">
@@ -3239,31 +3239,31 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>10</v>
+        <v>174</v>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>103.2</v>
       </c>
       <c r="O43" t="n">
-        <v>1200</v>
+        <v>10092</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>10034</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3304,31 +3304,31 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>185</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>102.7</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>111.5</v>
       </c>
       <c r="O44" t="n">
-        <v>1010</v>
+        <v>25530</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>26220</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="45">
@@ -3369,31 +3369,31 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>103.2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>102.7</v>
       </c>
       <c r="O45" t="n">
-        <v>1130</v>
+        <v>29212</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>30150</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="46">
@@ -3434,31 +3434,31 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>106.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>103.7</v>
       </c>
       <c r="O46" t="n">
-        <v>1490</v>
+        <v>12870</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>13650</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="47">
@@ -3499,31 +3499,31 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>10</v>
+        <v>276</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>97.8</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>89.7</v>
       </c>
       <c r="O47" t="n">
-        <v>810</v>
+        <v>31740</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>31050</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="48">
@@ -3564,31 +3564,31 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>313</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>111.8</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="O48" t="n">
-        <v>1160</v>
+        <v>19719</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>22050</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="49">
@@ -3629,31 +3629,31 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>101.5</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>92.3</v>
       </c>
       <c r="O49" t="n">
-        <v>1270</v>
+        <v>15244</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>15466</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="50">
@@ -3694,31 +3694,31 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>414</v>
+        <v>173</v>
       </c>
       <c r="J50" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K50" t="n">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="L50" t="n">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="M50" t="n">
-        <v>89.09999999999999</v>
+        <v>103.5</v>
       </c>
       <c r="N50" t="n">
-        <v>111.9</v>
+        <v>88.2</v>
       </c>
       <c r="O50" t="n">
-        <v>31050</v>
+        <v>19549</v>
       </c>
       <c r="P50" t="n">
-        <v>27675</v>
+        <v>20227</v>
       </c>
       <c r="Q50" t="n">
-        <v>89.09999999999999</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="51">
@@ -3759,31 +3759,31 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>319</v>
+        <v>208</v>
       </c>
       <c r="J51" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K51" t="n">
-        <v>301</v>
+        <v>230</v>
       </c>
       <c r="L51" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M51" t="n">
-        <v>94.40000000000001</v>
+        <v>110.6</v>
       </c>
       <c r="N51" t="n">
-        <v>91.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>46893</v>
+        <v>30160</v>
       </c>
       <c r="P51" t="n">
-        <v>44247</v>
+        <v>33350</v>
       </c>
       <c r="Q51" t="n">
-        <v>94.40000000000001</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="52">
@@ -3824,31 +3824,31 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>300</v>
+        <v>474</v>
       </c>
       <c r="J52" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="K52" t="n">
-        <v>284</v>
+        <v>478</v>
       </c>
       <c r="L52" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="M52" t="n">
-        <v>94.7</v>
+        <v>100.8</v>
       </c>
       <c r="N52" t="n">
-        <v>109.8</v>
+        <v>108.8</v>
       </c>
       <c r="O52" t="n">
-        <v>19800</v>
+        <v>47400</v>
       </c>
       <c r="P52" t="n">
-        <v>18744</v>
+        <v>47800</v>
       </c>
       <c r="Q52" t="n">
-        <v>94.7</v>
+        <v>100.8</v>
       </c>
     </row>
     <row r="53">
@@ -3889,31 +3889,31 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="J53" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="K53" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="L53" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="M53" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>112.7</v>
+        <v>112.3</v>
       </c>
       <c r="O53" t="n">
-        <v>22272</v>
+        <v>36312</v>
       </c>
       <c r="P53" t="n">
-        <v>22272</v>
+        <v>34443</v>
       </c>
       <c r="Q53" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -3954,31 +3954,31 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>416</v>
+        <v>162</v>
       </c>
       <c r="J54" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="K54" t="n">
-        <v>431</v>
+        <v>172</v>
       </c>
       <c r="L54" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="M54" t="n">
-        <v>103.6</v>
+        <v>106.2</v>
       </c>
       <c r="N54" t="n">
-        <v>113.2</v>
+        <v>90.2</v>
       </c>
       <c r="O54" t="n">
-        <v>55744</v>
+        <v>10854</v>
       </c>
       <c r="P54" t="n">
-        <v>57754</v>
+        <v>11524</v>
       </c>
       <c r="Q54" t="n">
-        <v>103.6</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="55">
@@ -4019,31 +4019,31 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>409</v>
+        <v>166</v>
       </c>
       <c r="J55" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="K55" t="n">
-        <v>376</v>
+        <v>158</v>
       </c>
       <c r="L55" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="M55" t="n">
-        <v>91.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="N55" t="n">
-        <v>86.3</v>
+        <v>97.2</v>
       </c>
       <c r="O55" t="n">
-        <v>27812</v>
+        <v>16268</v>
       </c>
       <c r="P55" t="n">
-        <v>25568</v>
+        <v>15484</v>
       </c>
       <c r="Q55" t="n">
-        <v>91.90000000000001</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="56">
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>276</v>
+        <v>383</v>
       </c>
       <c r="J56" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K56" t="n">
-        <v>244</v>
+        <v>359</v>
       </c>
       <c r="L56" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="M56" t="n">
-        <v>88.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="N56" t="n">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>16008</v>
+        <v>35619</v>
       </c>
       <c r="P56" t="n">
-        <v>14152</v>
+        <v>33387</v>
       </c>
       <c r="Q56" t="n">
-        <v>88.40000000000001</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="57">
@@ -4149,31 +4149,31 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="J57" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="K57" t="n">
-        <v>343</v>
+        <v>465</v>
       </c>
       <c r="L57" t="n">
-        <v>71</v>
+        <v>107</v>
       </c>
       <c r="M57" t="n">
-        <v>85.8</v>
+        <v>111.8</v>
       </c>
       <c r="N57" t="n">
-        <v>104.4</v>
+        <v>94.7</v>
       </c>
       <c r="O57" t="n">
-        <v>53200</v>
+        <v>51584</v>
       </c>
       <c r="P57" t="n">
-        <v>45619</v>
+        <v>57660</v>
       </c>
       <c r="Q57" t="n">
-        <v>85.8</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="58">
@@ -4214,31 +4214,31 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="J58" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="K58" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="L58" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="M58" t="n">
-        <v>92.8</v>
+        <v>89.8</v>
       </c>
       <c r="N58" t="n">
-        <v>88.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>16770</v>
+        <v>11968</v>
       </c>
       <c r="P58" t="n">
-        <v>15566</v>
+        <v>10752</v>
       </c>
       <c r="Q58" t="n">
-        <v>92.8</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="59">
@@ -4279,31 +4279,31 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="J59" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K59" t="n">
-        <v>197</v>
+        <v>93</v>
       </c>
       <c r="L59" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M59" t="n">
-        <v>91.2</v>
+        <v>112</v>
       </c>
       <c r="N59" t="n">
-        <v>96</v>
+        <v>94.7</v>
       </c>
       <c r="O59" t="n">
-        <v>16632</v>
+        <v>7719</v>
       </c>
       <c r="P59" t="n">
-        <v>15169</v>
+        <v>8649</v>
       </c>
       <c r="Q59" t="n">
-        <v>91.2</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60">
@@ -4344,31 +4344,31 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>162</v>
+        <v>435</v>
       </c>
       <c r="J60" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="K60" t="n">
-        <v>167</v>
+        <v>425</v>
       </c>
       <c r="L60" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="M60" t="n">
-        <v>103.1</v>
+        <v>97.7</v>
       </c>
       <c r="N60" t="n">
-        <v>113.2</v>
+        <v>95.5</v>
       </c>
       <c r="O60" t="n">
-        <v>18792</v>
+        <v>51330</v>
       </c>
       <c r="P60" t="n">
-        <v>19372</v>
+        <v>50150</v>
       </c>
       <c r="Q60" t="n">
-        <v>103.1</v>
+        <v>97.7</v>
       </c>
     </row>
     <row r="61">
@@ -4409,31 +4409,31 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>248</v>
+        <v>578</v>
       </c>
       <c r="J61" t="n">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="K61" t="n">
-        <v>221</v>
+        <v>502</v>
       </c>
       <c r="L61" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="M61" t="n">
-        <v>89.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>98.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="O61" t="n">
-        <v>17112</v>
+        <v>79186</v>
       </c>
       <c r="P61" t="n">
-        <v>15249</v>
+        <v>68774</v>
       </c>
       <c r="Q61" t="n">
-        <v>89.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4474,31 +4474,31 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>270</v>
+        <v>193</v>
       </c>
       <c r="J62" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="K62" t="n">
-        <v>235</v>
+        <v>177</v>
       </c>
       <c r="L62" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="M62" t="n">
-        <v>87</v>
+        <v>91.7</v>
       </c>
       <c r="N62" t="n">
-        <v>89.2</v>
+        <v>109.5</v>
       </c>
       <c r="O62" t="n">
-        <v>29700</v>
+        <v>27020</v>
       </c>
       <c r="P62" t="n">
-        <v>25850</v>
+        <v>24780</v>
       </c>
       <c r="Q62" t="n">
-        <v>87</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="63">
@@ -4539,31 +4539,31 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="J63" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="K63" t="n">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="L63" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="M63" t="n">
-        <v>108.8</v>
+        <v>110.5</v>
       </c>
       <c r="N63" t="n">
-        <v>95.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="O63" t="n">
-        <v>25585</v>
+        <v>21708</v>
       </c>
       <c r="P63" t="n">
-        <v>27846</v>
+        <v>23986</v>
       </c>
       <c r="Q63" t="n">
-        <v>108.8</v>
+        <v>110.5</v>
       </c>
     </row>
     <row r="64">
@@ -4604,31 +4604,31 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>289</v>
+        <v>422</v>
       </c>
       <c r="J64" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K64" t="n">
-        <v>287</v>
+        <v>408</v>
       </c>
       <c r="L64" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="M64" t="n">
-        <v>99.3</v>
+        <v>96.7</v>
       </c>
       <c r="N64" t="n">
-        <v>103.1</v>
+        <v>87.7</v>
       </c>
       <c r="O64" t="n">
-        <v>39015</v>
+        <v>29962</v>
       </c>
       <c r="P64" t="n">
-        <v>38745</v>
+        <v>28968</v>
       </c>
       <c r="Q64" t="n">
-        <v>99.3</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="65">
@@ -4669,31 +4669,31 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>196</v>
+        <v>461</v>
       </c>
       <c r="J65" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="K65" t="n">
-        <v>197</v>
+        <v>429</v>
       </c>
       <c r="L65" t="n">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="M65" t="n">
-        <v>100.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="N65" t="n">
-        <v>110.3</v>
+        <v>101.5</v>
       </c>
       <c r="O65" t="n">
-        <v>29400</v>
+        <v>66384</v>
       </c>
       <c r="P65" t="n">
-        <v>29550</v>
+        <v>61776</v>
       </c>
       <c r="Q65" t="n">
-        <v>100.5</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4734,31 +4734,31 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>174</v>
+        <v>281</v>
       </c>
       <c r="J66" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="K66" t="n">
-        <v>162</v>
+        <v>242</v>
       </c>
       <c r="L66" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="M66" t="n">
-        <v>93.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N66" t="n">
-        <v>95.7</v>
+        <v>90.7</v>
       </c>
       <c r="O66" t="n">
-        <v>15138</v>
+        <v>24728</v>
       </c>
       <c r="P66" t="n">
-        <v>14094</v>
+        <v>21296</v>
       </c>
       <c r="Q66" t="n">
-        <v>93.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -4799,31 +4799,31 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="J67" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="K67" t="n">
-        <v>154</v>
+        <v>266</v>
       </c>
       <c r="L67" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="M67" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N67" t="n">
-        <v>103.6</v>
+        <v>86.2</v>
       </c>
       <c r="O67" t="n">
-        <v>24780</v>
+        <v>38205</v>
       </c>
       <c r="P67" t="n">
-        <v>21560</v>
+        <v>35910</v>
       </c>
       <c r="Q67" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68">
@@ -4864,31 +4864,31 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>144</v>
+        <v>332</v>
       </c>
       <c r="J68" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="K68" t="n">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="L68" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="M68" t="n">
-        <v>93.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="N68" t="n">
-        <v>117.6</v>
+        <v>100</v>
       </c>
       <c r="O68" t="n">
-        <v>10512</v>
+        <v>32204</v>
       </c>
       <c r="P68" t="n">
-        <v>9782</v>
+        <v>30264</v>
       </c>
       <c r="Q68" t="n">
-        <v>93.09999999999999</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="J69" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="K69" t="n">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="L69" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="M69" t="n">
-        <v>105.4</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N69" t="n">
-        <v>89.7</v>
+        <v>95.8</v>
       </c>
       <c r="O69" t="n">
-        <v>6837</v>
+        <v>21631</v>
       </c>
       <c r="P69" t="n">
-        <v>7208</v>
+        <v>21437</v>
       </c>
       <c r="Q69" t="n">
-        <v>105.4</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -4994,31 +4994,31 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>478</v>
+        <v>244</v>
       </c>
       <c r="J70" t="n">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="K70" t="n">
-        <v>455</v>
+        <v>217</v>
       </c>
       <c r="L70" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="M70" t="n">
-        <v>95.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N70" t="n">
-        <v>98.7</v>
+        <v>87.3</v>
       </c>
       <c r="O70" t="n">
-        <v>49712</v>
+        <v>22448</v>
       </c>
       <c r="P70" t="n">
-        <v>47320</v>
+        <v>19964</v>
       </c>
       <c r="Q70" t="n">
-        <v>95.2</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5059,31 +5059,31 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>301</v>
+        <v>209</v>
       </c>
       <c r="J71" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>299</v>
+        <v>196</v>
       </c>
       <c r="L71" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="M71" t="n">
-        <v>99.3</v>
+        <v>93.8</v>
       </c>
       <c r="N71" t="n">
-        <v>86.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="O71" t="n">
-        <v>18963</v>
+        <v>30514</v>
       </c>
       <c r="P71" t="n">
-        <v>18837</v>
+        <v>28616</v>
       </c>
       <c r="Q71" t="n">
-        <v>99.3</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="72">
@@ -5124,31 +5124,31 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>421</v>
+        <v>512</v>
       </c>
       <c r="J72" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K72" t="n">
-        <v>395</v>
+        <v>495</v>
       </c>
       <c r="L72" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="M72" t="n">
-        <v>93.8</v>
+        <v>96.7</v>
       </c>
       <c r="N72" t="n">
-        <v>104.8</v>
+        <v>86</v>
       </c>
       <c r="O72" t="n">
-        <v>54309</v>
+        <v>73728</v>
       </c>
       <c r="P72" t="n">
-        <v>50955</v>
+        <v>71280</v>
       </c>
       <c r="Q72" t="n">
-        <v>93.8</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="73">
@@ -5189,31 +5189,31 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>263</v>
+        <v>406</v>
       </c>
       <c r="J73" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="K73" t="n">
-        <v>263</v>
+        <v>445</v>
       </c>
       <c r="L73" t="n">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="M73" t="n">
-        <v>100</v>
+        <v>109.6</v>
       </c>
       <c r="N73" t="n">
-        <v>87.2</v>
+        <v>95.3</v>
       </c>
       <c r="O73" t="n">
-        <v>32086</v>
+        <v>29232</v>
       </c>
       <c r="P73" t="n">
-        <v>32086</v>
+        <v>32040</v>
       </c>
       <c r="Q73" t="n">
-        <v>100</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="74">
@@ -5254,31 +5254,31 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="J74" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="L74" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M74" t="n">
-        <v>86.8</v>
+        <v>108.7</v>
       </c>
       <c r="N74" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
       <c r="O74" t="n">
-        <v>6307</v>
+        <v>11408</v>
       </c>
       <c r="P74" t="n">
-        <v>5474</v>
+        <v>12400</v>
       </c>
       <c r="Q74" t="n">
-        <v>86.8</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="75">
@@ -5319,31 +5319,31 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K75" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M75" t="n">
-        <v>88.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N75" t="n">
         <v>100</v>
       </c>
       <c r="O75" t="n">
-        <v>2268</v>
+        <v>9782</v>
       </c>
       <c r="P75" t="n">
-        <v>1998</v>
+        <v>9648</v>
       </c>
       <c r="Q75" t="n">
-        <v>88.09999999999999</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -5384,31 +5384,31 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>55</v>
+        <v>340</v>
       </c>
       <c r="J76" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="K76" t="n">
-        <v>52</v>
+        <v>296</v>
       </c>
       <c r="L76" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="M76" t="n">
-        <v>94.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N76" t="n">
-        <v>90</v>
+        <v>88.7</v>
       </c>
       <c r="O76" t="n">
-        <v>5555</v>
+        <v>20060</v>
       </c>
       <c r="P76" t="n">
-        <v>5252</v>
+        <v>17464</v>
       </c>
       <c r="Q76" t="n">
-        <v>94.5</v>
+        <v>87.09999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -5449,31 +5449,31 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>38</v>
+        <v>224</v>
       </c>
       <c r="J77" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="K77" t="n">
-        <v>37</v>
+        <v>199</v>
       </c>
       <c r="L77" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="M77" t="n">
-        <v>97.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="N77" t="n">
-        <v>90</v>
+        <v>103.4</v>
       </c>
       <c r="O77" t="n">
-        <v>2280</v>
+        <v>26656</v>
       </c>
       <c r="P77" t="n">
-        <v>2220</v>
+        <v>23681</v>
       </c>
       <c r="Q77" t="n">
-        <v>97.40000000000001</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="78">
@@ -5514,31 +5514,31 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J78" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K78" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="L78" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M78" t="n">
-        <v>98.5</v>
+        <v>108.1</v>
       </c>
       <c r="N78" t="n">
-        <v>107.7</v>
+        <v>100</v>
       </c>
       <c r="O78" t="n">
-        <v>8450</v>
+        <v>7918</v>
       </c>
       <c r="P78" t="n">
-        <v>8320</v>
+        <v>8560</v>
       </c>
       <c r="Q78" t="n">
-        <v>98.5</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="79">
@@ -5579,31 +5579,31 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="J79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K79" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="L79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
-        <v>86.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N79" t="n">
         <v>100</v>
       </c>
       <c r="O79" t="n">
-        <v>8364</v>
+        <v>5336</v>
       </c>
       <c r="P79" t="n">
-        <v>7242</v>
+        <v>4692</v>
       </c>
       <c r="Q79" t="n">
-        <v>86.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -5644,31 +5644,31 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>85</v>
+        <v>221</v>
       </c>
       <c r="J80" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="K80" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="L80" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="M80" t="n">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="N80" t="n">
-        <v>88.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O80" t="n">
-        <v>8925</v>
+        <v>18343</v>
       </c>
       <c r="P80" t="n">
-        <v>8925</v>
+        <v>16600</v>
       </c>
       <c r="Q80" t="n">
-        <v>100</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="81">
@@ -5709,31 +5709,31 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="J81" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="K81" t="n">
-        <v>67</v>
+        <v>216</v>
       </c>
       <c r="L81" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="M81" t="n">
-        <v>95.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N81" t="n">
-        <v>86.7</v>
+        <v>90.7</v>
       </c>
       <c r="O81" t="n">
-        <v>4830</v>
+        <v>21000</v>
       </c>
       <c r="P81" t="n">
-        <v>4623</v>
+        <v>18144</v>
       </c>
       <c r="Q81" t="n">
-        <v>95.7</v>
+        <v>86.40000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5774,31 +5774,31 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J82" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K82" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="L82" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M82" t="n">
-        <v>90.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="N82" t="n">
-        <v>100</v>
+        <v>108.3</v>
       </c>
       <c r="O82" t="n">
-        <v>12012</v>
+        <v>8701</v>
       </c>
       <c r="P82" t="n">
-        <v>10868</v>
+        <v>7797</v>
       </c>
       <c r="Q82" t="n">
-        <v>90.5</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -5839,31 +5839,31 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="J83" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K83" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L83" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M83" t="n">
-        <v>94.2</v>
+        <v>90.7</v>
       </c>
       <c r="N83" t="n">
-        <v>91.7</v>
+        <v>112.5</v>
       </c>
       <c r="O83" t="n">
-        <v>3450</v>
+        <v>7500</v>
       </c>
       <c r="P83" t="n">
-        <v>3250</v>
+        <v>6800</v>
       </c>
       <c r="Q83" t="n">
-        <v>94.2</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="84">
@@ -5904,31 +5904,31 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>65</v>
+        <v>245</v>
       </c>
       <c r="J84" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K84" t="n">
-        <v>67</v>
+        <v>209</v>
       </c>
       <c r="L84" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="M84" t="n">
-        <v>103.1</v>
+        <v>85.3</v>
       </c>
       <c r="N84" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="O84" t="n">
-        <v>5785</v>
+        <v>17885</v>
       </c>
       <c r="P84" t="n">
-        <v>5963</v>
+        <v>15257</v>
       </c>
       <c r="Q84" t="n">
-        <v>103.1</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="85">
@@ -5969,31 +5969,31 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>66</v>
+        <v>357</v>
       </c>
       <c r="J85" t="n">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="K85" t="n">
-        <v>65</v>
+        <v>326</v>
       </c>
       <c r="L85" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="M85" t="n">
-        <v>98.5</v>
+        <v>91.3</v>
       </c>
       <c r="N85" t="n">
-        <v>115.4</v>
+        <v>93.3</v>
       </c>
       <c r="O85" t="n">
-        <v>4620</v>
+        <v>27132</v>
       </c>
       <c r="P85" t="n">
-        <v>4550</v>
+        <v>24776</v>
       </c>
       <c r="Q85" t="n">
-        <v>98.5</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="86">
@@ -6034,31 +6034,31 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="J86" t="n">
         <v>14</v>
       </c>
       <c r="K86" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M86" t="n">
-        <v>104.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="N86" t="n">
-        <v>85.7</v>
+        <v>107.1</v>
       </c>
       <c r="O86" t="n">
-        <v>6432</v>
+        <v>10290</v>
       </c>
       <c r="P86" t="n">
-        <v>6700</v>
+        <v>9975</v>
       </c>
       <c r="Q86" t="n">
-        <v>104.2</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -6099,31 +6099,31 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="K87" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="L87" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M87" t="n">
-        <v>106.9</v>
+        <v>88.8</v>
       </c>
       <c r="N87" t="n">
-        <v>100</v>
+        <v>114.3</v>
       </c>
       <c r="O87" t="n">
-        <v>2610</v>
+        <v>5340</v>
       </c>
       <c r="P87" t="n">
-        <v>2790</v>
+        <v>4740</v>
       </c>
       <c r="Q87" t="n">
-        <v>106.9</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="88">
@@ -6164,31 +6164,31 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>52</v>
+        <v>362</v>
       </c>
       <c r="J88" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="K88" t="n">
-        <v>46</v>
+        <v>344</v>
       </c>
       <c r="L88" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="M88" t="n">
-        <v>88.5</v>
+        <v>95</v>
       </c>
       <c r="N88" t="n">
-        <v>116.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="O88" t="n">
-        <v>2912</v>
+        <v>40544</v>
       </c>
       <c r="P88" t="n">
-        <v>2576</v>
+        <v>38528</v>
       </c>
       <c r="Q88" t="n">
-        <v>88.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="89">
@@ -6229,31 +6229,31 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>60</v>
+        <v>248</v>
       </c>
       <c r="J89" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K89" t="n">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="L89" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="M89" t="n">
-        <v>98.3</v>
+        <v>88.7</v>
       </c>
       <c r="N89" t="n">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="O89" t="n">
-        <v>7920</v>
+        <v>23064</v>
       </c>
       <c r="P89" t="n">
-        <v>7788</v>
+        <v>20460</v>
       </c>
       <c r="Q89" t="n">
-        <v>98.3</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="90">
@@ -6294,31 +6294,31 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="J90" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K90" t="n">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="M90" t="n">
-        <v>108.3</v>
+        <v>95</v>
       </c>
       <c r="N90" t="n">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O90" t="n">
-        <v>3384</v>
+        <v>5200</v>
       </c>
       <c r="P90" t="n">
-        <v>3666</v>
+        <v>4940</v>
       </c>
       <c r="Q90" t="n">
-        <v>108.3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91">
@@ -6359,31 +6359,31 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="J91" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K91" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="M91" t="n">
-        <v>112.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N91" t="n">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O91" t="n">
-        <v>4672</v>
+        <v>18744</v>
       </c>
       <c r="P91" t="n">
-        <v>5256</v>
+        <v>17040</v>
       </c>
       <c r="Q91" t="n">
-        <v>112.5</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6424,28 +6424,28 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>43</v>
+        <v>253</v>
       </c>
       <c r="J92" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="K92" t="n">
-        <v>41</v>
+        <v>241</v>
       </c>
       <c r="L92" t="n">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="M92" t="n">
         <v>95.3</v>
       </c>
       <c r="N92" t="n">
-        <v>100</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O92" t="n">
-        <v>2365</v>
+        <v>15939</v>
       </c>
       <c r="P92" t="n">
-        <v>2255</v>
+        <v>15183</v>
       </c>
       <c r="Q92" t="n">
         <v>95.3</v>
@@ -6489,31 +6489,31 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>32</v>
+        <v>215</v>
       </c>
       <c r="J93" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="K93" t="n">
-        <v>35</v>
+        <v>213</v>
       </c>
       <c r="L93" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="M93" t="n">
-        <v>109.4</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N93" t="n">
-        <v>150</v>
+        <v>96.2</v>
       </c>
       <c r="O93" t="n">
-        <v>4128</v>
+        <v>20855</v>
       </c>
       <c r="P93" t="n">
-        <v>4515</v>
+        <v>20661</v>
       </c>
       <c r="Q93" t="n">
-        <v>109.4</v>
+        <v>99.09999999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6554,31 +6554,31 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="J94" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K94" t="n">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="L94" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M94" t="n">
-        <v>91.7</v>
+        <v>103.4</v>
       </c>
       <c r="N94" t="n">
-        <v>95</v>
+        <v>96.2</v>
       </c>
       <c r="O94" t="n">
-        <v>11928</v>
+        <v>12272</v>
       </c>
       <c r="P94" t="n">
-        <v>10934</v>
+        <v>12688</v>
       </c>
       <c r="Q94" t="n">
-        <v>91.7</v>
+        <v>103.4</v>
       </c>
     </row>
     <row r="95">
@@ -6619,31 +6619,31 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="J95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K95" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="L95" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>111.4</v>
+        <v>87</v>
       </c>
       <c r="N95" t="n">
-        <v>112.5</v>
+        <v>100</v>
       </c>
       <c r="O95" t="n">
-        <v>3885</v>
+        <v>5382</v>
       </c>
       <c r="P95" t="n">
-        <v>4329</v>
+        <v>4680</v>
       </c>
       <c r="Q95" t="n">
-        <v>111.4</v>
+        <v>87</v>
       </c>
     </row>
     <row r="96">
@@ -6684,31 +6684,31 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>64</v>
+        <v>236</v>
       </c>
       <c r="J96" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K96" t="n">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="L96" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="M96" t="n">
-        <v>107.8</v>
+        <v>89</v>
       </c>
       <c r="N96" t="n">
-        <v>100</v>
+        <v>102.9</v>
       </c>
       <c r="O96" t="n">
-        <v>4736</v>
+        <v>30680</v>
       </c>
       <c r="P96" t="n">
-        <v>5106</v>
+        <v>27300</v>
       </c>
       <c r="Q96" t="n">
-        <v>107.8</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97">
@@ -6749,31 +6749,31 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>55</v>
+        <v>294</v>
       </c>
       <c r="J97" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="K97" t="n">
-        <v>57</v>
+        <v>261</v>
       </c>
       <c r="L97" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="M97" t="n">
-        <v>103.6</v>
+        <v>88.8</v>
       </c>
       <c r="N97" t="n">
-        <v>112.5</v>
+        <v>104.4</v>
       </c>
       <c r="O97" t="n">
-        <v>4785</v>
+        <v>33516</v>
       </c>
       <c r="P97" t="n">
-        <v>4959</v>
+        <v>29754</v>
       </c>
       <c r="Q97" t="n">
-        <v>103.6</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="98">
@@ -6814,31 +6814,31 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="J98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K98" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="L98" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M98" t="n">
-        <v>88.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="N98" t="n">
-        <v>110</v>
+        <v>113.3</v>
       </c>
       <c r="O98" t="n">
-        <v>7276</v>
+        <v>16756</v>
       </c>
       <c r="P98" t="n">
-        <v>6420</v>
+        <v>16188</v>
       </c>
       <c r="Q98" t="n">
-        <v>88.2</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -6879,31 +6879,31 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="J99" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="K99" t="n">
-        <v>63</v>
+        <v>174</v>
       </c>
       <c r="L99" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M99" t="n">
-        <v>105</v>
+        <v>98.3</v>
       </c>
       <c r="N99" t="n">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O99" t="n">
-        <v>8940</v>
+        <v>26196</v>
       </c>
       <c r="P99" t="n">
-        <v>9387</v>
+        <v>25752</v>
       </c>
       <c r="Q99" t="n">
-        <v>105</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="100">
@@ -6944,31 +6944,31 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>41</v>
+        <v>292</v>
       </c>
       <c r="J100" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="K100" t="n">
-        <v>43</v>
+        <v>259</v>
       </c>
       <c r="L100" t="n">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="M100" t="n">
-        <v>104.9</v>
+        <v>88.7</v>
       </c>
       <c r="N100" t="n">
-        <v>100</v>
+        <v>103.3</v>
       </c>
       <c r="O100" t="n">
-        <v>4346</v>
+        <v>19272</v>
       </c>
       <c r="P100" t="n">
-        <v>4558</v>
+        <v>17094</v>
       </c>
       <c r="Q100" t="n">
-        <v>104.9</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="101">
@@ -7009,31 +7009,31 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>51</v>
+        <v>262</v>
       </c>
       <c r="J101" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="K101" t="n">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="L101" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="M101" t="n">
-        <v>92.2</v>
+        <v>92.7</v>
       </c>
       <c r="N101" t="n">
-        <v>100</v>
+        <v>115.2</v>
       </c>
       <c r="O101" t="n">
-        <v>3366</v>
+        <v>37990</v>
       </c>
       <c r="P101" t="n">
-        <v>3102</v>
+        <v>35235</v>
       </c>
       <c r="Q101" t="n">
-        <v>92.2</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="102">
@@ -7074,31 +7074,31 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="J102" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K102" t="n">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="L102" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="M102" t="n">
-        <v>90.40000000000001</v>
+        <v>109.8</v>
       </c>
       <c r="N102" t="n">
-        <v>105.9</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="O102" t="n">
-        <v>6032</v>
+        <v>18450</v>
       </c>
       <c r="P102" t="n">
-        <v>5452</v>
+        <v>20250</v>
       </c>
       <c r="Q102" t="n">
-        <v>90.40000000000001</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="103">
@@ -7139,31 +7139,31 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>41</v>
+        <v>226</v>
       </c>
       <c r="J103" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K103" t="n">
-        <v>36</v>
+        <v>215</v>
       </c>
       <c r="L103" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="M103" t="n">
-        <v>87.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="N103" t="n">
-        <v>87.5</v>
+        <v>114.3</v>
       </c>
       <c r="O103" t="n">
-        <v>5658</v>
+        <v>26668</v>
       </c>
       <c r="P103" t="n">
-        <v>4968</v>
+        <v>25370</v>
       </c>
       <c r="Q103" t="n">
-        <v>87.8</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -7204,31 +7204,31 @@
         </is>
       </c>
       <c r="I104" t="n">
+        <v>312</v>
+      </c>
+      <c r="J104" t="n">
+        <v>84</v>
+      </c>
+      <c r="K104" t="n">
+        <v>340</v>
+      </c>
+      <c r="L104" t="n">
         <v>80</v>
       </c>
-      <c r="J104" t="n">
-        <v>18</v>
-      </c>
-      <c r="K104" t="n">
-        <v>71</v>
-      </c>
-      <c r="L104" t="n">
-        <v>18</v>
-      </c>
       <c r="M104" t="n">
-        <v>88.8</v>
+        <v>109</v>
       </c>
       <c r="N104" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="O104" t="n">
-        <v>4720</v>
+        <v>34320</v>
       </c>
       <c r="P104" t="n">
-        <v>4189</v>
+        <v>37400</v>
       </c>
       <c r="Q104" t="n">
-        <v>88.8</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105">
@@ -7269,31 +7269,31 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>55</v>
+        <v>298</v>
       </c>
       <c r="J105" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="K105" t="n">
-        <v>50</v>
+        <v>307</v>
       </c>
       <c r="L105" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="M105" t="n">
-        <v>90.90000000000001</v>
+        <v>103</v>
       </c>
       <c r="N105" t="n">
-        <v>100</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="O105" t="n">
-        <v>8250</v>
+        <v>26820</v>
       </c>
       <c r="P105" t="n">
-        <v>7500</v>
+        <v>27630</v>
       </c>
       <c r="Q105" t="n">
-        <v>90.90000000000001</v>
+        <v>103</v>
       </c>
     </row>
     <row r="106">
@@ -7334,31 +7334,31 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="J106" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="K106" t="n">
-        <v>47</v>
+        <v>90</v>
       </c>
       <c r="L106" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M106" t="n">
-        <v>97.90000000000001</v>
+        <v>102.3</v>
       </c>
       <c r="N106" t="n">
-        <v>120</v>
+        <v>107.1</v>
       </c>
       <c r="O106" t="n">
-        <v>6624</v>
+        <v>9152</v>
       </c>
       <c r="P106" t="n">
-        <v>6486</v>
+        <v>9360</v>
       </c>
       <c r="Q106" t="n">
-        <v>97.90000000000001</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="107">
@@ -7399,31 +7399,31 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="J107" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="K107" t="n">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="L107" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="M107" t="n">
-        <v>97.09999999999999</v>
+        <v>112.6</v>
       </c>
       <c r="N107" t="n">
-        <v>100</v>
+        <v>111.8</v>
       </c>
       <c r="O107" t="n">
-        <v>3325</v>
+        <v>17667</v>
       </c>
       <c r="P107" t="n">
-        <v>3230</v>
+        <v>19890</v>
       </c>
       <c r="Q107" t="n">
-        <v>97.09999999999999</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="108">
@@ -7464,31 +7464,31 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>40</v>
+        <v>208</v>
       </c>
       <c r="J108" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K108" t="n">
-        <v>45</v>
+        <v>213</v>
       </c>
       <c r="L108" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="M108" t="n">
-        <v>112.5</v>
+        <v>102.4</v>
       </c>
       <c r="N108" t="n">
         <v>100</v>
       </c>
       <c r="O108" t="n">
-        <v>5360</v>
+        <v>12896</v>
       </c>
       <c r="P108" t="n">
-        <v>6030</v>
+        <v>13206</v>
       </c>
       <c r="Q108" t="n">
-        <v>112.5</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="109">
@@ -7529,31 +7529,31 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="J109" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="K109" t="n">
-        <v>44</v>
+        <v>217</v>
       </c>
       <c r="L109" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="M109" t="n">
-        <v>110</v>
+        <v>88.2</v>
       </c>
       <c r="N109" t="n">
-        <v>100</v>
+        <v>91.8</v>
       </c>
       <c r="O109" t="n">
-        <v>3760</v>
+        <v>13530</v>
       </c>
       <c r="P109" t="n">
-        <v>4136</v>
+        <v>11935</v>
       </c>
       <c r="Q109" t="n">
-        <v>110</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="110">
@@ -7594,31 +7594,31 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="J110" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K110" t="n">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="L110" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M110" t="n">
-        <v>111.4</v>
+        <v>103.9</v>
       </c>
       <c r="N110" t="n">
         <v>112.5</v>
       </c>
       <c r="O110" t="n">
-        <v>2590</v>
+        <v>8576</v>
       </c>
       <c r="P110" t="n">
-        <v>2886</v>
+        <v>8911</v>
       </c>
       <c r="Q110" t="n">
-        <v>111.4</v>
+        <v>103.9</v>
       </c>
     </row>
     <row r="111">
@@ -7659,31 +7659,31 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="J111" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="K111" t="n">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="L111" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="M111" t="n">
-        <v>86.7</v>
+        <v>103.2</v>
       </c>
       <c r="N111" t="n">
-        <v>118.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O111" t="n">
-        <v>3540</v>
+        <v>11856</v>
       </c>
       <c r="P111" t="n">
-        <v>3068</v>
+        <v>12236</v>
       </c>
       <c r="Q111" t="n">
-        <v>86.7</v>
+        <v>103.2</v>
       </c>
     </row>
     <row r="112">
@@ -7724,31 +7724,31 @@
         </is>
       </c>
       <c r="I112" t="n">
+        <v>176</v>
+      </c>
+      <c r="J112" t="n">
         <v>34</v>
       </c>
-      <c r="J112" t="n">
-        <v>5</v>
-      </c>
       <c r="K112" t="n">
-        <v>33</v>
+        <v>176</v>
       </c>
       <c r="L112" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M112" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="N112" t="n">
-        <v>120</v>
+        <v>88.2</v>
       </c>
       <c r="O112" t="n">
-        <v>1700</v>
+        <v>24464</v>
       </c>
       <c r="P112" t="n">
-        <v>1650</v>
+        <v>24464</v>
       </c>
       <c r="Q112" t="n">
-        <v>97.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113">
@@ -7789,31 +7789,31 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="J113" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K113" t="n">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="L113" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="M113" t="n">
-        <v>101.9</v>
+        <v>89.7</v>
       </c>
       <c r="N113" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O113" t="n">
-        <v>3120</v>
+        <v>16264</v>
       </c>
       <c r="P113" t="n">
-        <v>3180</v>
+        <v>14592</v>
       </c>
       <c r="Q113" t="n">
-        <v>101.9</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="114">
@@ -7854,31 +7854,31 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="J114" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K114" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="L114" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M114" t="n">
-        <v>91.5</v>
+        <v>100.7</v>
       </c>
       <c r="N114" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="O114" t="n">
-        <v>7462</v>
+        <v>15052</v>
       </c>
       <c r="P114" t="n">
-        <v>6825</v>
+        <v>15158</v>
       </c>
       <c r="Q114" t="n">
-        <v>91.5</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="115">
@@ -7919,31 +7919,31 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="J115" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="K115" t="n">
-        <v>62</v>
+        <v>154</v>
       </c>
       <c r="L115" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M115" t="n">
-        <v>87.3</v>
+        <v>110.8</v>
       </c>
       <c r="N115" t="n">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="O115" t="n">
-        <v>5964</v>
+        <v>15985</v>
       </c>
       <c r="P115" t="n">
-        <v>5208</v>
+        <v>17710</v>
       </c>
       <c r="Q115" t="n">
-        <v>87.3</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="116">
@@ -7984,31 +7984,31 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="J116" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="K116" t="n">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="L116" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="M116" t="n">
-        <v>92.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="N116" t="n">
         <v>100</v>
       </c>
       <c r="O116" t="n">
-        <v>7560</v>
+        <v>13284</v>
       </c>
       <c r="P116" t="n">
-        <v>7020</v>
+        <v>12150</v>
       </c>
       <c r="Q116" t="n">
-        <v>92.90000000000001</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="117">
@@ -8049,31 +8049,31 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="J117" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K117" t="n">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="L117" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="M117" t="n">
-        <v>101.4</v>
+        <v>106.6</v>
       </c>
       <c r="N117" t="n">
-        <v>100</v>
+        <v>105.9</v>
       </c>
       <c r="O117" t="n">
-        <v>4416</v>
+        <v>19479</v>
       </c>
       <c r="P117" t="n">
-        <v>4480</v>
+        <v>20769</v>
       </c>
       <c r="Q117" t="n">
-        <v>101.4</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="118">
@@ -8114,31 +8114,31 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>112</v>
+        <v>185</v>
       </c>
       <c r="J118" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="K118" t="n">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="L118" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="M118" t="n">
-        <v>86.59999999999999</v>
+        <v>111.4</v>
       </c>
       <c r="N118" t="n">
-        <v>118.8</v>
+        <v>115.6</v>
       </c>
       <c r="O118" t="n">
-        <v>12544</v>
+        <v>17020</v>
       </c>
       <c r="P118" t="n">
-        <v>10864</v>
+        <v>18952</v>
       </c>
       <c r="Q118" t="n">
-        <v>86.59999999999999</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="119">
@@ -8179,31 +8179,31 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="J119" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="K119" t="n">
-        <v>113</v>
+        <v>242</v>
       </c>
       <c r="L119" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="M119" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="N119" t="n">
-        <v>117.6</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O119" t="n">
-        <v>10922</v>
+        <v>36792</v>
       </c>
       <c r="P119" t="n">
-        <v>9718</v>
+        <v>35332</v>
       </c>
       <c r="Q119" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120">
@@ -8244,31 +8244,31 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="J120" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="K120" t="n">
-        <v>86</v>
+        <v>309</v>
       </c>
       <c r="L120" t="n">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="M120" t="n">
-        <v>114.7</v>
+        <v>88.5</v>
       </c>
       <c r="N120" t="n">
-        <v>105.3</v>
+        <v>100</v>
       </c>
       <c r="O120" t="n">
-        <v>3825</v>
+        <v>33504</v>
       </c>
       <c r="P120" t="n">
-        <v>4386</v>
+        <v>29664</v>
       </c>
       <c r="Q120" t="n">
-        <v>114.7</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="121">
@@ -8309,31 +8309,31 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>77</v>
+        <v>346</v>
       </c>
       <c r="J121" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="K121" t="n">
-        <v>71</v>
+        <v>324</v>
       </c>
       <c r="L121" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="M121" t="n">
-        <v>92.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="N121" t="n">
-        <v>111.1</v>
+        <v>104</v>
       </c>
       <c r="O121" t="n">
-        <v>6853</v>
+        <v>46710</v>
       </c>
       <c r="P121" t="n">
-        <v>6319</v>
+        <v>43740</v>
       </c>
       <c r="Q121" t="n">
-        <v>92.2</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="122">
@@ -8374,31 +8374,31 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="J122" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K122" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L122" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M122" t="n">
-        <v>109.4</v>
+        <v>105.3</v>
       </c>
       <c r="N122" t="n">
-        <v>107.1</v>
+        <v>100</v>
       </c>
       <c r="O122" t="n">
-        <v>3328</v>
+        <v>7425</v>
       </c>
       <c r="P122" t="n">
-        <v>3640</v>
+        <v>7821</v>
       </c>
       <c r="Q122" t="n">
-        <v>109.4</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="123">
@@ -8439,31 +8439,31 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="J123" t="n">
+        <v>14</v>
+      </c>
+      <c r="K123" t="n">
+        <v>81</v>
+      </c>
+      <c r="L123" t="n">
         <v>15</v>
       </c>
-      <c r="K123" t="n">
-        <v>96</v>
-      </c>
-      <c r="L123" t="n">
-        <v>16</v>
-      </c>
       <c r="M123" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N123" t="n">
-        <v>106.7</v>
+        <v>107.1</v>
       </c>
       <c r="O123" t="n">
-        <v>16950</v>
+        <v>10192</v>
       </c>
       <c r="P123" t="n">
-        <v>14400</v>
+        <v>9072</v>
       </c>
       <c r="Q123" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="124">
@@ -8504,31 +8504,31 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>86</v>
+        <v>234</v>
       </c>
       <c r="J124" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="K124" t="n">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="L124" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="M124" t="n">
-        <v>91.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="N124" t="n">
-        <v>110</v>
+        <v>103.6</v>
       </c>
       <c r="O124" t="n">
-        <v>5160</v>
+        <v>14976</v>
       </c>
       <c r="P124" t="n">
-        <v>4740</v>
+        <v>14272</v>
       </c>
       <c r="Q124" t="n">
-        <v>91.90000000000001</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="125">
@@ -8569,31 +8569,31 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="J125" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="K125" t="n">
-        <v>61</v>
+        <v>205</v>
       </c>
       <c r="L125" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M125" t="n">
-        <v>89.7</v>
+        <v>110.2</v>
       </c>
       <c r="N125" t="n">
-        <v>116.7</v>
+        <v>106.2</v>
       </c>
       <c r="O125" t="n">
-        <v>5168</v>
+        <v>18600</v>
       </c>
       <c r="P125" t="n">
-        <v>4636</v>
+        <v>20500</v>
       </c>
       <c r="Q125" t="n">
-        <v>89.7</v>
+        <v>110.2</v>
       </c>
     </row>
     <row r="126">
@@ -8634,31 +8634,31 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="J126" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="K126" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="L126" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="M126" t="n">
-        <v>95.2</v>
+        <v>86</v>
       </c>
       <c r="N126" t="n">
-        <v>110</v>
+        <v>95.8</v>
       </c>
       <c r="O126" t="n">
-        <v>4340</v>
+        <v>14338</v>
       </c>
       <c r="P126" t="n">
-        <v>4130</v>
+        <v>12328</v>
       </c>
       <c r="Q126" t="n">
-        <v>95.2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="127">
@@ -8699,31 +8699,31 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="J127" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="K127" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="L127" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M127" t="n">
-        <v>90.2</v>
+        <v>109.6</v>
       </c>
       <c r="N127" t="n">
         <v>100</v>
       </c>
       <c r="O127" t="n">
-        <v>2805</v>
+        <v>6640</v>
       </c>
       <c r="P127" t="n">
-        <v>2530</v>
+        <v>7280</v>
       </c>
       <c r="Q127" t="n">
-        <v>90.2</v>
+        <v>109.6</v>
       </c>
     </row>
     <row r="128">
@@ -8764,31 +8764,31 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>55</v>
+        <v>148</v>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="K128" t="n">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="L128" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="M128" t="n">
-        <v>105.5</v>
+        <v>98</v>
       </c>
       <c r="N128" t="n">
-        <v>125</v>
+        <v>110.7</v>
       </c>
       <c r="O128" t="n">
-        <v>6545</v>
+        <v>7844</v>
       </c>
       <c r="P128" t="n">
-        <v>6902</v>
+        <v>7685</v>
       </c>
       <c r="Q128" t="n">
-        <v>105.5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="129">
@@ -8829,31 +8829,31 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>64</v>
+        <v>162</v>
       </c>
       <c r="J129" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K129" t="n">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="L129" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M129" t="n">
-        <v>96.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="N129" t="n">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="O129" t="n">
-        <v>5440</v>
+        <v>16686</v>
       </c>
       <c r="P129" t="n">
-        <v>5270</v>
+        <v>14729</v>
       </c>
       <c r="Q129" t="n">
-        <v>96.90000000000001</v>
+        <v>88.3</v>
       </c>
     </row>
     <row r="130">
@@ -8894,31 +8894,31 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="J130" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K130" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L130" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M130" t="n">
-        <v>94.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="N130" t="n">
-        <v>94.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="O130" t="n">
-        <v>3536</v>
+        <v>6222</v>
       </c>
       <c r="P130" t="n">
-        <v>3328</v>
+        <v>5304</v>
       </c>
       <c r="Q130" t="n">
-        <v>94.09999999999999</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="131">
@@ -8959,31 +8959,31 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="J131" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K131" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L131" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="M131" t="n">
-        <v>92.90000000000001</v>
+        <v>114.9</v>
       </c>
       <c r="N131" t="n">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O131" t="n">
-        <v>4335</v>
+        <v>4089</v>
       </c>
       <c r="P131" t="n">
-        <v>4029</v>
+        <v>4698</v>
       </c>
       <c r="Q131" t="n">
-        <v>92.90000000000001</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="132">
@@ -9024,31 +9024,31 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="J132" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K132" t="n">
-        <v>94</v>
+        <v>236</v>
       </c>
       <c r="L132" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="M132" t="n">
-        <v>109.3</v>
+        <v>107.3</v>
       </c>
       <c r="N132" t="n">
-        <v>110</v>
+        <v>113.5</v>
       </c>
       <c r="O132" t="n">
-        <v>10922</v>
+        <v>18040</v>
       </c>
       <c r="P132" t="n">
-        <v>11938</v>
+        <v>19352</v>
       </c>
       <c r="Q132" t="n">
-        <v>109.3</v>
+        <v>107.3</v>
       </c>
     </row>
     <row r="133">
@@ -9089,31 +9089,31 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>57</v>
+        <v>218</v>
       </c>
       <c r="J133" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="K133" t="n">
-        <v>53</v>
+        <v>228</v>
       </c>
       <c r="L133" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="M133" t="n">
-        <v>93</v>
+        <v>104.6</v>
       </c>
       <c r="N133" t="n">
-        <v>122.2</v>
+        <v>89.7</v>
       </c>
       <c r="O133" t="n">
-        <v>5586</v>
+        <v>29866</v>
       </c>
       <c r="P133" t="n">
-        <v>5194</v>
+        <v>31236</v>
       </c>
       <c r="Q133" t="n">
-        <v>93</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="134">
@@ -9154,31 +9154,31 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="J134" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K134" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="L134" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M134" t="n">
-        <v>106.5</v>
+        <v>100</v>
       </c>
       <c r="N134" t="n">
-        <v>100</v>
+        <v>115.4</v>
       </c>
       <c r="O134" t="n">
-        <v>3906</v>
+        <v>4158</v>
       </c>
       <c r="P134" t="n">
         <v>4158</v>
       </c>
       <c r="Q134" t="n">
-        <v>106.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135">
@@ -9219,31 +9219,31 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="J135" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K135" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="L135" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M135" t="n">
-        <v>108.6</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N135" t="n">
-        <v>114.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O135" t="n">
-        <v>2800</v>
+        <v>8190</v>
       </c>
       <c r="P135" t="n">
-        <v>3040</v>
+        <v>7735</v>
       </c>
       <c r="Q135" t="n">
-        <v>108.6</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="136">
@@ -9284,31 +9284,31 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>67</v>
+        <v>267</v>
       </c>
       <c r="J136" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="K136" t="n">
-        <v>69</v>
+        <v>250</v>
       </c>
       <c r="L136" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="M136" t="n">
-        <v>103</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="N136" t="n">
-        <v>100</v>
+        <v>106.5</v>
       </c>
       <c r="O136" t="n">
-        <v>5025</v>
+        <v>31506</v>
       </c>
       <c r="P136" t="n">
-        <v>5175</v>
+        <v>29500</v>
       </c>
       <c r="Q136" t="n">
-        <v>103</v>
+        <v>93.59999999999999</v>
       </c>
     </row>
     <row r="137">
@@ -9349,31 +9349,31 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>46</v>
+        <v>244</v>
       </c>
       <c r="J137" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="K137" t="n">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="L137" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="M137" t="n">
-        <v>113</v>
+        <v>87.7</v>
       </c>
       <c r="N137" t="n">
-        <v>112.5</v>
+        <v>95.2</v>
       </c>
       <c r="O137" t="n">
-        <v>5014</v>
+        <v>21472</v>
       </c>
       <c r="P137" t="n">
-        <v>5668</v>
+        <v>18832</v>
       </c>
       <c r="Q137" t="n">
-        <v>113</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="138">
@@ -9414,31 +9414,31 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="J138" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K138" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="L138" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M138" t="n">
-        <v>104.1</v>
+        <v>100</v>
       </c>
       <c r="N138" t="n">
-        <v>92.3</v>
+        <v>111.1</v>
       </c>
       <c r="O138" t="n">
-        <v>5586</v>
+        <v>6887</v>
       </c>
       <c r="P138" t="n">
-        <v>5814</v>
+        <v>6887</v>
       </c>
       <c r="Q138" t="n">
-        <v>104.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139">
@@ -9479,31 +9479,31 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="J139" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K139" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="L139" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="M139" t="n">
-        <v>87.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="N139" t="n">
-        <v>88.90000000000001</v>
+        <v>115.8</v>
       </c>
       <c r="O139" t="n">
-        <v>6027</v>
+        <v>14580</v>
       </c>
       <c r="P139" t="n">
-        <v>5292</v>
+        <v>12555</v>
       </c>
       <c r="Q139" t="n">
-        <v>87.8</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="140">
@@ -9544,31 +9544,31 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="J140" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="K140" t="n">
-        <v>41</v>
+        <v>254</v>
       </c>
       <c r="L140" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="M140" t="n">
-        <v>91.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="N140" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="O140" t="n">
-        <v>2475</v>
+        <v>29792</v>
       </c>
       <c r="P140" t="n">
-        <v>2255</v>
+        <v>28448</v>
       </c>
       <c r="Q140" t="n">
-        <v>91.09999999999999</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="141">
@@ -9609,31 +9609,31 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>51</v>
+        <v>361</v>
       </c>
       <c r="J141" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="K141" t="n">
-        <v>50</v>
+        <v>308</v>
       </c>
       <c r="L141" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="M141" t="n">
-        <v>98</v>
+        <v>85.3</v>
       </c>
       <c r="N141" t="n">
-        <v>91.7</v>
+        <v>113.8</v>
       </c>
       <c r="O141" t="n">
-        <v>6171</v>
+        <v>24548</v>
       </c>
       <c r="P141" t="n">
-        <v>6050</v>
+        <v>20944</v>
       </c>
       <c r="Q141" t="n">
-        <v>98</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="142">
@@ -9674,31 +9674,31 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="J142" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K142" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="L142" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M142" t="n">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="N142" t="n">
-        <v>87</v>
+        <v>107.7</v>
       </c>
       <c r="O142" t="n">
-        <v>12726</v>
+        <v>4958</v>
       </c>
       <c r="P142" t="n">
-        <v>12474</v>
+        <v>4891</v>
       </c>
       <c r="Q142" t="n">
-        <v>98</v>
+        <v>98.59999999999999</v>
       </c>
     </row>
     <row r="143">
@@ -9739,31 +9739,31 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="J143" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K143" t="n">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="L143" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="M143" t="n">
-        <v>108.8</v>
+        <v>86.7</v>
       </c>
       <c r="N143" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="O143" t="n">
-        <v>9588</v>
+        <v>7119</v>
       </c>
       <c r="P143" t="n">
-        <v>10434</v>
+        <v>6174</v>
       </c>
       <c r="Q143" t="n">
-        <v>108.8</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="144">
@@ -9804,31 +9804,31 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="J144" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="K144" t="n">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="L144" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M144" t="n">
-        <v>111.4</v>
+        <v>104.9</v>
       </c>
       <c r="N144" t="n">
-        <v>100</v>
+        <v>105.3</v>
       </c>
       <c r="O144" t="n">
-        <v>2684</v>
+        <v>11928</v>
       </c>
       <c r="P144" t="n">
-        <v>2989</v>
+        <v>12516</v>
       </c>
       <c r="Q144" t="n">
-        <v>111.4</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="145">
@@ -9869,31 +9869,31 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="J145" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="K145" t="n">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="L145" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="M145" t="n">
-        <v>96.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N145" t="n">
-        <v>93.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O145" t="n">
-        <v>14628</v>
+        <v>23932</v>
       </c>
       <c r="P145" t="n">
-        <v>14076</v>
+        <v>23560</v>
       </c>
       <c r="Q145" t="n">
-        <v>96.2</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -9934,31 +9934,31 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1016</v>
+        <v>125</v>
       </c>
       <c r="J146" t="n">
-        <v>245</v>
+        <v>29</v>
       </c>
       <c r="K146" t="n">
-        <v>951</v>
+        <v>132</v>
       </c>
       <c r="L146" t="n">
-        <v>209</v>
+        <v>30</v>
       </c>
       <c r="M146" t="n">
-        <v>93.59999999999999</v>
+        <v>105.6</v>
       </c>
       <c r="N146" t="n">
-        <v>85.3</v>
+        <v>103.4</v>
       </c>
       <c r="O146" t="n">
-        <v>79248</v>
+        <v>9625</v>
       </c>
       <c r="P146" t="n">
-        <v>74178</v>
+        <v>10164</v>
       </c>
       <c r="Q146" t="n">
-        <v>93.59999999999999</v>
+        <v>105.6</v>
       </c>
     </row>
     <row r="147">
@@ -9999,31 +9999,31 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1028</v>
+        <v>218</v>
       </c>
       <c r="J147" t="n">
-        <v>250</v>
+        <v>42</v>
       </c>
       <c r="K147" t="n">
-        <v>1138</v>
+        <v>189</v>
       </c>
       <c r="L147" t="n">
-        <v>266</v>
+        <v>40</v>
       </c>
       <c r="M147" t="n">
-        <v>110.7</v>
+        <v>86.7</v>
       </c>
       <c r="N147" t="n">
-        <v>106.4</v>
+        <v>95.2</v>
       </c>
       <c r="O147" t="n">
-        <v>69904</v>
+        <v>26814</v>
       </c>
       <c r="P147" t="n">
-        <v>77384</v>
+        <v>23247</v>
       </c>
       <c r="Q147" t="n">
-        <v>110.7</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="148">
@@ -10064,31 +10064,31 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1118</v>
+        <v>393</v>
       </c>
       <c r="J148" t="n">
-        <v>190</v>
+        <v>53</v>
       </c>
       <c r="K148" t="n">
-        <v>996</v>
+        <v>352</v>
       </c>
       <c r="L148" t="n">
-        <v>192</v>
+        <v>53</v>
       </c>
       <c r="M148" t="n">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="N148" t="n">
-        <v>101.1</v>
+        <v>100</v>
       </c>
       <c r="O148" t="n">
-        <v>69316</v>
+        <v>39693</v>
       </c>
       <c r="P148" t="n">
-        <v>61752</v>
+        <v>35552</v>
       </c>
       <c r="Q148" t="n">
-        <v>89.09999999999999</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="149">
@@ -10129,31 +10129,31 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1077</v>
+        <v>261</v>
       </c>
       <c r="J149" t="n">
-        <v>230</v>
+        <v>45</v>
       </c>
       <c r="K149" t="n">
-        <v>1099</v>
+        <v>273</v>
       </c>
       <c r="L149" t="n">
-        <v>239</v>
+        <v>41</v>
       </c>
       <c r="M149" t="n">
-        <v>102</v>
+        <v>104.6</v>
       </c>
       <c r="N149" t="n">
-        <v>103.9</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O149" t="n">
-        <v>100161</v>
+        <v>34974</v>
       </c>
       <c r="P149" t="n">
-        <v>102207</v>
+        <v>36582</v>
       </c>
       <c r="Q149" t="n">
-        <v>102</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="150">
@@ -10194,31 +10194,31 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1024</v>
+        <v>208</v>
       </c>
       <c r="J150" t="n">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="K150" t="n">
-        <v>977</v>
+        <v>183</v>
       </c>
       <c r="L150" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="M150" t="n">
-        <v>95.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="N150" t="n">
-        <v>101.9</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O150" t="n">
-        <v>103424</v>
+        <v>28704</v>
       </c>
       <c r="P150" t="n">
-        <v>98677</v>
+        <v>25254</v>
       </c>
       <c r="Q150" t="n">
-        <v>95.40000000000001</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151">
@@ -10259,31 +10259,31 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1019</v>
+        <v>221</v>
       </c>
       <c r="J151" t="n">
-        <v>235</v>
+        <v>36</v>
       </c>
       <c r="K151" t="n">
-        <v>1071</v>
+        <v>192</v>
       </c>
       <c r="L151" t="n">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c r="M151" t="n">
-        <v>105.1</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="N151" t="n">
-        <v>93.2</v>
+        <v>97.2</v>
       </c>
       <c r="O151" t="n">
-        <v>65216</v>
+        <v>15912</v>
       </c>
       <c r="P151" t="n">
-        <v>68544</v>
+        <v>13824</v>
       </c>
       <c r="Q151" t="n">
-        <v>105.1</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="152">
@@ -10324,31 +10324,31 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>952</v>
+        <v>281</v>
       </c>
       <c r="J152" t="n">
-        <v>169</v>
+        <v>54</v>
       </c>
       <c r="K152" t="n">
-        <v>900</v>
+        <v>273</v>
       </c>
       <c r="L152" t="n">
-        <v>169</v>
+        <v>49</v>
       </c>
       <c r="M152" t="n">
-        <v>94.5</v>
+        <v>97.2</v>
       </c>
       <c r="N152" t="n">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="O152" t="n">
-        <v>82824</v>
+        <v>23885</v>
       </c>
       <c r="P152" t="n">
-        <v>78300</v>
+        <v>23205</v>
       </c>
       <c r="Q152" t="n">
-        <v>94.5</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="153">
@@ -10389,31 +10389,31 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1140</v>
+        <v>313</v>
       </c>
       <c r="J153" t="n">
-        <v>226</v>
+        <v>64</v>
       </c>
       <c r="K153" t="n">
-        <v>968</v>
+        <v>270</v>
       </c>
       <c r="L153" t="n">
-        <v>202</v>
+        <v>62</v>
       </c>
       <c r="M153" t="n">
-        <v>84.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="N153" t="n">
-        <v>89.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O153" t="n">
-        <v>155040</v>
+        <v>46011</v>
       </c>
       <c r="P153" t="n">
-        <v>131648</v>
+        <v>39690</v>
       </c>
       <c r="Q153" t="n">
-        <v>84.90000000000001</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="154">
@@ -10454,31 +10454,31 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1241</v>
+        <v>133</v>
       </c>
       <c r="J154" t="n">
-        <v>174</v>
+        <v>31</v>
       </c>
       <c r="K154" t="n">
-        <v>1055</v>
+        <v>139</v>
       </c>
       <c r="L154" t="n">
-        <v>189</v>
+        <v>32</v>
       </c>
       <c r="M154" t="n">
-        <v>85</v>
+        <v>104.5</v>
       </c>
       <c r="N154" t="n">
-        <v>108.6</v>
+        <v>103.2</v>
       </c>
       <c r="O154" t="n">
-        <v>111690</v>
+        <v>12502</v>
       </c>
       <c r="P154" t="n">
-        <v>94950</v>
+        <v>13066</v>
       </c>
       <c r="Q154" t="n">
-        <v>85</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="155">
@@ -10519,31 +10519,31 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1034</v>
+        <v>103</v>
       </c>
       <c r="J155" t="n">
-        <v>253</v>
+        <v>21</v>
       </c>
       <c r="K155" t="n">
-        <v>1091</v>
+        <v>113</v>
       </c>
       <c r="L155" t="n">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="M155" t="n">
-        <v>105.5</v>
+        <v>109.7</v>
       </c>
       <c r="N155" t="n">
-        <v>87</v>
+        <v>95.2</v>
       </c>
       <c r="O155" t="n">
-        <v>140624</v>
+        <v>15244</v>
       </c>
       <c r="P155" t="n">
-        <v>148376</v>
+        <v>16724</v>
       </c>
       <c r="Q155" t="n">
-        <v>105.5</v>
+        <v>109.7</v>
       </c>
     </row>
     <row r="156">
@@ -10584,31 +10584,31 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>829</v>
+        <v>389</v>
       </c>
       <c r="J156" t="n">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="K156" t="n">
-        <v>940</v>
+        <v>398</v>
       </c>
       <c r="L156" t="n">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="M156" t="n">
-        <v>113.4</v>
+        <v>102.3</v>
       </c>
       <c r="N156" t="n">
-        <v>97.7</v>
+        <v>90.8</v>
       </c>
       <c r="O156" t="n">
-        <v>69636</v>
+        <v>42012</v>
       </c>
       <c r="P156" t="n">
-        <v>78960</v>
+        <v>42984</v>
       </c>
       <c r="Q156" t="n">
-        <v>113.4</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="157">
@@ -10649,31 +10649,31 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1026</v>
+        <v>267</v>
       </c>
       <c r="J157" t="n">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="K157" t="n">
-        <v>1038</v>
+        <v>290</v>
       </c>
       <c r="L157" t="n">
-        <v>173</v>
+        <v>41</v>
       </c>
       <c r="M157" t="n">
-        <v>101.2</v>
+        <v>108.6</v>
       </c>
       <c r="N157" t="n">
-        <v>104.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="O157" t="n">
-        <v>113886</v>
+        <v>28836</v>
       </c>
       <c r="P157" t="n">
-        <v>115218</v>
+        <v>31320</v>
       </c>
       <c r="Q157" t="n">
-        <v>101.2</v>
+        <v>108.6</v>
       </c>
     </row>
     <row r="158">
@@ -10714,31 +10714,31 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1061</v>
+        <v>103</v>
       </c>
       <c r="J158" t="n">
-        <v>221</v>
+        <v>16</v>
       </c>
       <c r="K158" t="n">
-        <v>967</v>
+        <v>108</v>
       </c>
       <c r="L158" t="n">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="M158" t="n">
-        <v>91.09999999999999</v>
+        <v>104.9</v>
       </c>
       <c r="N158" t="n">
-        <v>86</v>
+        <v>112.5</v>
       </c>
       <c r="O158" t="n">
-        <v>60477</v>
+        <v>13596</v>
       </c>
       <c r="P158" t="n">
-        <v>55119</v>
+        <v>14256</v>
       </c>
       <c r="Q158" t="n">
-        <v>91.09999999999999</v>
+        <v>104.9</v>
       </c>
     </row>
     <row r="159">
@@ -10779,31 +10779,31 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1115</v>
+        <v>113</v>
       </c>
       <c r="J159" t="n">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="K159" t="n">
-        <v>979</v>
+        <v>97</v>
       </c>
       <c r="L159" t="n">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="M159" t="n">
-        <v>87.8</v>
+        <v>85.8</v>
       </c>
       <c r="N159" t="n">
-        <v>92.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="O159" t="n">
-        <v>151640</v>
+        <v>13673</v>
       </c>
       <c r="P159" t="n">
-        <v>133144</v>
+        <v>11737</v>
       </c>
       <c r="Q159" t="n">
-        <v>87.8</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="160">
@@ -10844,31 +10844,31 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1323</v>
+        <v>291</v>
       </c>
       <c r="J160" t="n">
-        <v>268</v>
+        <v>45</v>
       </c>
       <c r="K160" t="n">
-        <v>1190</v>
+        <v>248</v>
       </c>
       <c r="L160" t="n">
-        <v>232</v>
+        <v>41</v>
       </c>
       <c r="M160" t="n">
-        <v>89.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="N160" t="n">
-        <v>86.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O160" t="n">
-        <v>99225</v>
+        <v>42486</v>
       </c>
       <c r="P160" t="n">
-        <v>89250</v>
+        <v>36208</v>
       </c>
       <c r="Q160" t="n">
-        <v>89.90000000000001</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="161">
@@ -10909,31 +10909,31 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>956</v>
+        <v>321</v>
       </c>
       <c r="J161" t="n">
-        <v>258</v>
+        <v>48</v>
       </c>
       <c r="K161" t="n">
-        <v>1058</v>
+        <v>323</v>
       </c>
       <c r="L161" t="n">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="M161" t="n">
-        <v>110.7</v>
+        <v>100.6</v>
       </c>
       <c r="N161" t="n">
-        <v>90.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="O161" t="n">
-        <v>83172</v>
+        <v>26964</v>
       </c>
       <c r="P161" t="n">
-        <v>92046</v>
+        <v>27132</v>
       </c>
       <c r="Q161" t="n">
-        <v>110.7</v>
+        <v>100.6</v>
       </c>
     </row>
     <row r="162">
@@ -10974,31 +10974,31 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1074</v>
+        <v>119</v>
       </c>
       <c r="J162" t="n">
-        <v>159</v>
+        <v>16</v>
       </c>
       <c r="K162" t="n">
-        <v>1078</v>
+        <v>107</v>
       </c>
       <c r="L162" t="n">
-        <v>177</v>
+        <v>15</v>
       </c>
       <c r="M162" t="n">
-        <v>100.4</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N162" t="n">
-        <v>111.3</v>
+        <v>93.8</v>
       </c>
       <c r="O162" t="n">
-        <v>138546</v>
+        <v>6426</v>
       </c>
       <c r="P162" t="n">
-        <v>139062</v>
+        <v>5778</v>
       </c>
       <c r="Q162" t="n">
-        <v>100.4</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="163">
@@ -11039,31 +11039,31 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1232</v>
+        <v>107</v>
       </c>
       <c r="J163" t="n">
-        <v>268</v>
+        <v>22</v>
       </c>
       <c r="K163" t="n">
-        <v>1172</v>
+        <v>114</v>
       </c>
       <c r="L163" t="n">
-        <v>244</v>
+        <v>19</v>
       </c>
       <c r="M163" t="n">
-        <v>95.09999999999999</v>
+        <v>106.5</v>
       </c>
       <c r="N163" t="n">
-        <v>91</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O163" t="n">
-        <v>151536</v>
+        <v>13375</v>
       </c>
       <c r="P163" t="n">
-        <v>144156</v>
+        <v>14250</v>
       </c>
       <c r="Q163" t="n">
-        <v>95.09999999999999</v>
+        <v>106.5</v>
       </c>
     </row>
     <row r="164">
@@ -11104,31 +11104,31 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1062</v>
+        <v>309</v>
       </c>
       <c r="J164" t="n">
-        <v>249</v>
+        <v>62</v>
       </c>
       <c r="K164" t="n">
-        <v>1105</v>
+        <v>300</v>
       </c>
       <c r="L164" t="n">
-        <v>218</v>
+        <v>60</v>
       </c>
       <c r="M164" t="n">
-        <v>104</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N164" t="n">
-        <v>87.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="O164" t="n">
-        <v>118944</v>
+        <v>17922</v>
       </c>
       <c r="P164" t="n">
-        <v>123760</v>
+        <v>17400</v>
       </c>
       <c r="Q164" t="n">
-        <v>104</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -11169,31 +11169,31 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1243</v>
+        <v>364</v>
       </c>
       <c r="J165" t="n">
-        <v>266</v>
+        <v>74</v>
       </c>
       <c r="K165" t="n">
-        <v>1109</v>
+        <v>353</v>
       </c>
       <c r="L165" t="n">
-        <v>226</v>
+        <v>79</v>
       </c>
       <c r="M165" t="n">
-        <v>89.2</v>
+        <v>97</v>
       </c>
       <c r="N165" t="n">
-        <v>85</v>
+        <v>106.8</v>
       </c>
       <c r="O165" t="n">
-        <v>82038</v>
+        <v>40040</v>
       </c>
       <c r="P165" t="n">
-        <v>73194</v>
+        <v>38830</v>
       </c>
       <c r="Q165" t="n">
-        <v>89.2</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166">
@@ -11234,31 +11234,31 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1245</v>
+        <v>83</v>
       </c>
       <c r="J166" t="n">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="K166" t="n">
-        <v>1091</v>
+        <v>82</v>
       </c>
       <c r="L166" t="n">
-        <v>202</v>
+        <v>16</v>
       </c>
       <c r="M166" t="n">
-        <v>87.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="N166" t="n">
-        <v>107.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="O166" t="n">
-        <v>113295</v>
+        <v>9545</v>
       </c>
       <c r="P166" t="n">
-        <v>99281</v>
+        <v>9430</v>
       </c>
       <c r="Q166" t="n">
-        <v>87.59999999999999</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="167">
@@ -11299,31 +11299,31 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1250</v>
+        <v>79</v>
       </c>
       <c r="J167" t="n">
-        <v>216</v>
+        <v>17</v>
       </c>
       <c r="K167" t="n">
-        <v>1146</v>
+        <v>84</v>
       </c>
       <c r="L167" t="n">
-        <v>206</v>
+        <v>18</v>
       </c>
       <c r="M167" t="n">
-        <v>91.7</v>
+        <v>106.3</v>
       </c>
       <c r="N167" t="n">
-        <v>95.40000000000001</v>
+        <v>105.9</v>
       </c>
       <c r="O167" t="n">
-        <v>62500</v>
+        <v>7979</v>
       </c>
       <c r="P167" t="n">
-        <v>57300</v>
+        <v>8484</v>
       </c>
       <c r="Q167" t="n">
-        <v>91.7</v>
+        <v>106.3</v>
       </c>
     </row>
     <row r="168">
@@ -11364,31 +11364,31 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1122</v>
+        <v>316</v>
       </c>
       <c r="J168" t="n">
-        <v>233</v>
+        <v>68</v>
       </c>
       <c r="K168" t="n">
-        <v>1135</v>
+        <v>328</v>
       </c>
       <c r="L168" t="n">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="M168" t="n">
-        <v>101.2</v>
+        <v>103.8</v>
       </c>
       <c r="N168" t="n">
-        <v>85.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="O168" t="n">
-        <v>75174</v>
+        <v>16116</v>
       </c>
       <c r="P168" t="n">
-        <v>76045</v>
+        <v>16728</v>
       </c>
       <c r="Q168" t="n">
-        <v>101.2</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="169">
@@ -11429,31 +11429,31 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>1232</v>
+        <v>284</v>
       </c>
       <c r="J169" t="n">
-        <v>199</v>
+        <v>38</v>
       </c>
       <c r="K169" t="n">
-        <v>1116</v>
+        <v>252</v>
       </c>
       <c r="L169" t="n">
-        <v>221</v>
+        <v>42</v>
       </c>
       <c r="M169" t="n">
-        <v>90.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="N169" t="n">
-        <v>111.1</v>
+        <v>110.5</v>
       </c>
       <c r="O169" t="n">
-        <v>145376</v>
+        <v>40044</v>
       </c>
       <c r="P169" t="n">
-        <v>131688</v>
+        <v>35532</v>
       </c>
       <c r="Q169" t="n">
-        <v>90.59999999999999</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="170">
@@ -11494,31 +11494,31 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>883</v>
+        <v>258</v>
       </c>
       <c r="J170" t="n">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="K170" t="n">
-        <v>911</v>
+        <v>293</v>
       </c>
       <c r="L170" t="n">
-        <v>160</v>
+        <v>67</v>
       </c>
       <c r="M170" t="n">
-        <v>103.2</v>
+        <v>113.6</v>
       </c>
       <c r="N170" t="n">
-        <v>108.8</v>
+        <v>113.6</v>
       </c>
       <c r="O170" t="n">
-        <v>98896</v>
+        <v>16512</v>
       </c>
       <c r="P170" t="n">
-        <v>102032</v>
+        <v>18752</v>
       </c>
       <c r="Q170" t="n">
-        <v>103.2</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="171">
@@ -11559,31 +11559,31 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>813</v>
+        <v>327</v>
       </c>
       <c r="J171" t="n">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="K171" t="n">
-        <v>724</v>
+        <v>282</v>
       </c>
       <c r="L171" t="n">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="M171" t="n">
-        <v>89.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="N171" t="n">
-        <v>87.09999999999999</v>
+        <v>101.7</v>
       </c>
       <c r="O171" t="n">
-        <v>40650</v>
+        <v>37605</v>
       </c>
       <c r="P171" t="n">
-        <v>36200</v>
+        <v>32430</v>
       </c>
       <c r="Q171" t="n">
-        <v>89.09999999999999</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="172">
@@ -11624,31 +11624,31 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>815</v>
+        <v>438</v>
       </c>
       <c r="J172" t="n">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="K172" t="n">
-        <v>863</v>
+        <v>389</v>
       </c>
       <c r="L172" t="n">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="M172" t="n">
-        <v>105.9</v>
+        <v>88.8</v>
       </c>
       <c r="N172" t="n">
-        <v>100.6</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="O172" t="n">
-        <v>82315</v>
+        <v>22776</v>
       </c>
       <c r="P172" t="n">
-        <v>87163</v>
+        <v>20228</v>
       </c>
       <c r="Q172" t="n">
-        <v>105.9</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="173">
@@ -11689,31 +11689,31 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>765</v>
+        <v>314</v>
       </c>
       <c r="J173" t="n">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="K173" t="n">
-        <v>856</v>
+        <v>336</v>
       </c>
       <c r="L173" t="n">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="M173" t="n">
-        <v>111.9</v>
+        <v>107</v>
       </c>
       <c r="N173" t="n">
-        <v>86.59999999999999</v>
+        <v>110</v>
       </c>
       <c r="O173" t="n">
-        <v>42840</v>
+        <v>21038</v>
       </c>
       <c r="P173" t="n">
-        <v>47936</v>
+        <v>22512</v>
       </c>
       <c r="Q173" t="n">
-        <v>111.9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="174">
@@ -11754,31 +11754,31 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>572</v>
+        <v>302</v>
       </c>
       <c r="J174" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K174" t="n">
-        <v>574</v>
+        <v>307</v>
       </c>
       <c r="L174" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="M174" t="n">
-        <v>100.3</v>
+        <v>101.7</v>
       </c>
       <c r="N174" t="n">
-        <v>112.2</v>
+        <v>89.8</v>
       </c>
       <c r="O174" t="n">
-        <v>57200</v>
+        <v>16610</v>
       </c>
       <c r="P174" t="n">
-        <v>57400</v>
+        <v>16885</v>
       </c>
       <c r="Q174" t="n">
-        <v>100.3</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="175">
@@ -11819,31 +11819,31 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>543</v>
+        <v>325</v>
       </c>
       <c r="J175" t="n">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="K175" t="n">
-        <v>571</v>
+        <v>281</v>
       </c>
       <c r="L175" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="M175" t="n">
-        <v>105.2</v>
+        <v>86.5</v>
       </c>
       <c r="N175" t="n">
-        <v>88.90000000000001</v>
+        <v>111.5</v>
       </c>
       <c r="O175" t="n">
-        <v>52671</v>
+        <v>23075</v>
       </c>
       <c r="P175" t="n">
-        <v>55387</v>
+        <v>19951</v>
       </c>
       <c r="Q175" t="n">
-        <v>105.2</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="176">
@@ -11884,31 +11884,31 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>525</v>
+        <v>222</v>
       </c>
       <c r="J176" t="n">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="K176" t="n">
-        <v>588</v>
+        <v>195</v>
       </c>
       <c r="L176" t="n">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="M176" t="n">
-        <v>112</v>
+        <v>87.8</v>
       </c>
       <c r="N176" t="n">
-        <v>91.3</v>
+        <v>107.4</v>
       </c>
       <c r="O176" t="n">
-        <v>69300</v>
+        <v>13320</v>
       </c>
       <c r="P176" t="n">
-        <v>77616</v>
+        <v>11700</v>
       </c>
       <c r="Q176" t="n">
-        <v>112</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="177">
@@ -11949,31 +11949,31 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>619</v>
+        <v>275</v>
       </c>
       <c r="J177" t="n">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="K177" t="n">
-        <v>683</v>
+        <v>259</v>
       </c>
       <c r="L177" t="n">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="M177" t="n">
-        <v>110.3</v>
+        <v>94.2</v>
       </c>
       <c r="N177" t="n">
-        <v>93.7</v>
+        <v>91.7</v>
       </c>
       <c r="O177" t="n">
-        <v>51996</v>
+        <v>26125</v>
       </c>
       <c r="P177" t="n">
-        <v>57372</v>
+        <v>24605</v>
       </c>
       <c r="Q177" t="n">
-        <v>110.3</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="178">
@@ -12014,31 +12014,31 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>748</v>
+        <v>315</v>
       </c>
       <c r="J178" t="n">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="K178" t="n">
-        <v>662</v>
+        <v>311</v>
       </c>
       <c r="L178" t="n">
-        <v>128</v>
+        <v>60</v>
       </c>
       <c r="M178" t="n">
-        <v>88.5</v>
+        <v>98.7</v>
       </c>
       <c r="N178" t="n">
-        <v>94.09999999999999</v>
+        <v>109.1</v>
       </c>
       <c r="O178" t="n">
-        <v>93500</v>
+        <v>26460</v>
       </c>
       <c r="P178" t="n">
-        <v>82750</v>
+        <v>26124</v>
       </c>
       <c r="Q178" t="n">
-        <v>88.5</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="179">
@@ -12079,31 +12079,31 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>523</v>
+        <v>345</v>
       </c>
       <c r="J179" t="n">
-        <v>117</v>
+        <v>51</v>
       </c>
       <c r="K179" t="n">
-        <v>571</v>
+        <v>312</v>
       </c>
       <c r="L179" t="n">
-        <v>103</v>
+        <v>57</v>
       </c>
       <c r="M179" t="n">
-        <v>109.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="N179" t="n">
-        <v>88</v>
+        <v>111.8</v>
       </c>
       <c r="O179" t="n">
-        <v>65375</v>
+        <v>19665</v>
       </c>
       <c r="P179" t="n">
-        <v>71375</v>
+        <v>17784</v>
       </c>
       <c r="Q179" t="n">
-        <v>109.2</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="180">
@@ -12144,31 +12144,31 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>540</v>
+        <v>411</v>
       </c>
       <c r="J180" t="n">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="K180" t="n">
-        <v>605</v>
+        <v>377</v>
       </c>
       <c r="L180" t="n">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="M180" t="n">
-        <v>112</v>
+        <v>91.7</v>
       </c>
       <c r="N180" t="n">
-        <v>109.3</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="O180" t="n">
-        <v>38340</v>
+        <v>51375</v>
       </c>
       <c r="P180" t="n">
-        <v>42955</v>
+        <v>47125</v>
       </c>
       <c r="Q180" t="n">
-        <v>112</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="181">
@@ -12209,31 +12209,31 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>527</v>
+        <v>298</v>
       </c>
       <c r="J181" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="K181" t="n">
-        <v>588</v>
+        <v>264</v>
       </c>
       <c r="L181" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="M181" t="n">
-        <v>111.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N181" t="n">
-        <v>90.8</v>
+        <v>106</v>
       </c>
       <c r="O181" t="n">
-        <v>69037</v>
+        <v>36356</v>
       </c>
       <c r="P181" t="n">
-        <v>77028</v>
+        <v>32208</v>
       </c>
       <c r="Q181" t="n">
-        <v>111.6</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="182">
@@ -12274,31 +12274,31 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>670</v>
+        <v>461</v>
       </c>
       <c r="J182" t="n">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="K182" t="n">
-        <v>755</v>
+        <v>489</v>
       </c>
       <c r="L182" t="n">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="M182" t="n">
-        <v>112.7</v>
+        <v>106.1</v>
       </c>
       <c r="N182" t="n">
-        <v>101.5</v>
+        <v>104.5</v>
       </c>
       <c r="O182" t="n">
-        <v>34840</v>
+        <v>68689</v>
       </c>
       <c r="P182" t="n">
-        <v>39260</v>
+        <v>72861</v>
       </c>
       <c r="Q182" t="n">
-        <v>112.7</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="183">
@@ -12339,31 +12339,31 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>755</v>
+        <v>302</v>
       </c>
       <c r="J183" t="n">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="K183" t="n">
-        <v>711</v>
+        <v>318</v>
       </c>
       <c r="L183" t="n">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="M183" t="n">
-        <v>94.2</v>
+        <v>105.3</v>
       </c>
       <c r="N183" t="n">
-        <v>102.4</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O183" t="n">
-        <v>104190</v>
+        <v>17818</v>
       </c>
       <c r="P183" t="n">
-        <v>98118</v>
+        <v>18762</v>
       </c>
       <c r="Q183" t="n">
-        <v>94.2</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="184">
@@ -12404,31 +12404,31 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>587</v>
+        <v>178</v>
       </c>
       <c r="J184" t="n">
-        <v>131</v>
+        <v>46</v>
       </c>
       <c r="K184" t="n">
-        <v>625</v>
+        <v>199</v>
       </c>
       <c r="L184" t="n">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="M184" t="n">
-        <v>106.5</v>
+        <v>111.8</v>
       </c>
       <c r="N184" t="n">
-        <v>86.3</v>
+        <v>97.8</v>
       </c>
       <c r="O184" t="n">
-        <v>85702</v>
+        <v>22784</v>
       </c>
       <c r="P184" t="n">
-        <v>91250</v>
+        <v>25472</v>
       </c>
       <c r="Q184" t="n">
-        <v>106.5</v>
+        <v>111.8</v>
       </c>
     </row>
     <row r="185">
@@ -12469,31 +12469,31 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>692</v>
+        <v>135</v>
       </c>
       <c r="J185" t="n">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="K185" t="n">
-        <v>699</v>
+        <v>139</v>
       </c>
       <c r="L185" t="n">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="M185" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N185" t="n">
-        <v>98.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O185" t="n">
-        <v>87192</v>
+        <v>9180</v>
       </c>
       <c r="P185" t="n">
-        <v>88074</v>
+        <v>9452</v>
       </c>
       <c r="Q185" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="186">
@@ -12534,31 +12534,31 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>578</v>
+        <v>213</v>
       </c>
       <c r="J186" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="K186" t="n">
-        <v>584</v>
+        <v>231</v>
       </c>
       <c r="L186" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="M186" t="n">
-        <v>101</v>
+        <v>108.5</v>
       </c>
       <c r="N186" t="n">
-        <v>88</v>
+        <v>104.4</v>
       </c>
       <c r="O186" t="n">
-        <v>71094</v>
+        <v>23217</v>
       </c>
       <c r="P186" t="n">
-        <v>71832</v>
+        <v>25179</v>
       </c>
       <c r="Q186" t="n">
-        <v>101</v>
+        <v>108.5</v>
       </c>
     </row>
     <row r="187">
@@ -12599,31 +12599,31 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>639</v>
+        <v>173</v>
       </c>
       <c r="J187" t="n">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="K187" t="n">
-        <v>595</v>
+        <v>195</v>
       </c>
       <c r="L187" t="n">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="M187" t="n">
-        <v>93.09999999999999</v>
+        <v>112.7</v>
       </c>
       <c r="N187" t="n">
-        <v>107.1</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O187" t="n">
-        <v>63900</v>
+        <v>20933</v>
       </c>
       <c r="P187" t="n">
-        <v>59500</v>
+        <v>23595</v>
       </c>
       <c r="Q187" t="n">
-        <v>93.09999999999999</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="188">
@@ -12664,31 +12664,31 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>498</v>
+        <v>295</v>
       </c>
       <c r="J188" t="n">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="K188" t="n">
-        <v>559</v>
+        <v>289</v>
       </c>
       <c r="L188" t="n">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="M188" t="n">
-        <v>112.2</v>
+        <v>98</v>
       </c>
       <c r="N188" t="n">
-        <v>93.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="O188" t="n">
-        <v>58764</v>
+        <v>24190</v>
       </c>
       <c r="P188" t="n">
-        <v>65962</v>
+        <v>23698</v>
       </c>
       <c r="Q188" t="n">
-        <v>112.2</v>
+        <v>98</v>
       </c>
     </row>
     <row r="189">
@@ -12729,31 +12729,31 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>558</v>
+        <v>496</v>
       </c>
       <c r="J189" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K189" t="n">
-        <v>553</v>
+        <v>436</v>
       </c>
       <c r="L189" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M189" t="n">
-        <v>99.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="N189" t="n">
-        <v>109.9</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="O189" t="n">
-        <v>60822</v>
+        <v>37696</v>
       </c>
       <c r="P189" t="n">
-        <v>60277</v>
+        <v>33136</v>
       </c>
       <c r="Q189" t="n">
-        <v>99.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="190">
@@ -12794,31 +12794,31 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>815</v>
+        <v>367</v>
       </c>
       <c r="J190" t="n">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="K190" t="n">
-        <v>828</v>
+        <v>393</v>
       </c>
       <c r="L190" t="n">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="M190" t="n">
-        <v>101.6</v>
+        <v>107.1</v>
       </c>
       <c r="N190" t="n">
-        <v>89.3</v>
+        <v>101</v>
       </c>
       <c r="O190" t="n">
-        <v>92095</v>
+        <v>41471</v>
       </c>
       <c r="P190" t="n">
-        <v>93564</v>
+        <v>44409</v>
       </c>
       <c r="Q190" t="n">
-        <v>101.6</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="191">
@@ -12859,31 +12859,31 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1124</v>
+        <v>407</v>
       </c>
       <c r="J191" t="n">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="K191" t="n">
-        <v>969</v>
+        <v>360</v>
       </c>
       <c r="L191" t="n">
-        <v>187</v>
+        <v>57</v>
       </c>
       <c r="M191" t="n">
-        <v>86.2</v>
+        <v>88.5</v>
       </c>
       <c r="N191" t="n">
-        <v>93</v>
+        <v>90.5</v>
       </c>
       <c r="O191" t="n">
-        <v>92168</v>
+        <v>29711</v>
       </c>
       <c r="P191" t="n">
-        <v>79458</v>
+        <v>26280</v>
       </c>
       <c r="Q191" t="n">
-        <v>86.2</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="192">
@@ -12924,31 +12924,31 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>790</v>
+        <v>249</v>
       </c>
       <c r="J192" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="K192" t="n">
-        <v>704</v>
+        <v>258</v>
       </c>
       <c r="L192" t="n">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="M192" t="n">
-        <v>89.09999999999999</v>
+        <v>103.6</v>
       </c>
       <c r="N192" t="n">
-        <v>85.40000000000001</v>
+        <v>106.2</v>
       </c>
       <c r="O192" t="n">
-        <v>98750</v>
+        <v>34362</v>
       </c>
       <c r="P192" t="n">
-        <v>88000</v>
+        <v>35604</v>
       </c>
       <c r="Q192" t="n">
-        <v>89.09999999999999</v>
+        <v>103.6</v>
       </c>
     </row>
     <row r="193">
@@ -12989,31 +12989,31 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>981</v>
+        <v>345</v>
       </c>
       <c r="J193" t="n">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="K193" t="n">
-        <v>842</v>
+        <v>322</v>
       </c>
       <c r="L193" t="n">
-        <v>173</v>
+        <v>64</v>
       </c>
       <c r="M193" t="n">
-        <v>85.8</v>
+        <v>93.3</v>
       </c>
       <c r="N193" t="n">
-        <v>112.3</v>
+        <v>106.7</v>
       </c>
       <c r="O193" t="n">
-        <v>84366</v>
+        <v>35535</v>
       </c>
       <c r="P193" t="n">
-        <v>72412</v>
+        <v>33166</v>
       </c>
       <c r="Q193" t="n">
-        <v>85.8</v>
+        <v>93.3</v>
       </c>
     </row>
     <row r="194">
@@ -13054,31 +13054,31 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>840</v>
+        <v>242</v>
       </c>
       <c r="J194" t="n">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="K194" t="n">
-        <v>761</v>
+        <v>267</v>
       </c>
       <c r="L194" t="n">
-        <v>173</v>
+        <v>34</v>
       </c>
       <c r="M194" t="n">
-        <v>90.59999999999999</v>
+        <v>110.3</v>
       </c>
       <c r="N194" t="n">
-        <v>85.59999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="O194" t="n">
-        <v>72240</v>
+        <v>31218</v>
       </c>
       <c r="P194" t="n">
-        <v>65446</v>
+        <v>34443</v>
       </c>
       <c r="Q194" t="n">
-        <v>90.59999999999999</v>
+        <v>110.3</v>
       </c>
     </row>
     <row r="195">
@@ -13119,31 +13119,31 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>757</v>
+        <v>242</v>
       </c>
       <c r="J195" t="n">
-        <v>182</v>
+        <v>51</v>
       </c>
       <c r="K195" t="n">
-        <v>696</v>
+        <v>271</v>
       </c>
       <c r="L195" t="n">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="M195" t="n">
-        <v>91.90000000000001</v>
+        <v>112</v>
       </c>
       <c r="N195" t="n">
-        <v>86.8</v>
+        <v>107.8</v>
       </c>
       <c r="O195" t="n">
-        <v>59046</v>
+        <v>23716</v>
       </c>
       <c r="P195" t="n">
-        <v>54288</v>
+        <v>26558</v>
       </c>
       <c r="Q195" t="n">
-        <v>91.90000000000001</v>
+        <v>112</v>
       </c>
     </row>
     <row r="196">
@@ -13184,31 +13184,31 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>709</v>
+        <v>309</v>
       </c>
       <c r="J196" t="n">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="K196" t="n">
-        <v>686</v>
+        <v>298</v>
       </c>
       <c r="L196" t="n">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="M196" t="n">
-        <v>96.8</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N196" t="n">
-        <v>109.8</v>
+        <v>111.6</v>
       </c>
       <c r="O196" t="n">
-        <v>36868</v>
+        <v>30282</v>
       </c>
       <c r="P196" t="n">
-        <v>35672</v>
+        <v>29204</v>
       </c>
       <c r="Q196" t="n">
-        <v>96.8</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="197">
@@ -13249,31 +13249,31 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>669</v>
+        <v>232</v>
       </c>
       <c r="J197" t="n">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="K197" t="n">
-        <v>626</v>
+        <v>246</v>
       </c>
       <c r="L197" t="n">
-        <v>108</v>
+        <v>36</v>
       </c>
       <c r="M197" t="n">
-        <v>93.59999999999999</v>
+        <v>106</v>
       </c>
       <c r="N197" t="n">
-        <v>110.2</v>
+        <v>100</v>
       </c>
       <c r="O197" t="n">
-        <v>80280</v>
+        <v>16008</v>
       </c>
       <c r="P197" t="n">
-        <v>75120</v>
+        <v>16974</v>
       </c>
       <c r="Q197" t="n">
-        <v>93.59999999999999</v>
+        <v>106</v>
       </c>
     </row>
     <row r="198">
@@ -13314,31 +13314,31 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>656</v>
+        <v>222</v>
       </c>
       <c r="J198" t="n">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="K198" t="n">
-        <v>620</v>
+        <v>213</v>
       </c>
       <c r="L198" t="n">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="M198" t="n">
-        <v>94.5</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="N198" t="n">
-        <v>102.1</v>
+        <v>100</v>
       </c>
       <c r="O198" t="n">
-        <v>61664</v>
+        <v>29526</v>
       </c>
       <c r="P198" t="n">
-        <v>58280</v>
+        <v>28329</v>
       </c>
       <c r="Q198" t="n">
-        <v>94.5</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -13379,31 +13379,31 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>601</v>
+        <v>245</v>
       </c>
       <c r="J199" t="n">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="K199" t="n">
-        <v>579</v>
+        <v>264</v>
       </c>
       <c r="L199" t="n">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="M199" t="n">
-        <v>96.3</v>
+        <v>107.8</v>
       </c>
       <c r="N199" t="n">
-        <v>103.9</v>
+        <v>87.5</v>
       </c>
       <c r="O199" t="n">
-        <v>51686</v>
+        <v>16905</v>
       </c>
       <c r="P199" t="n">
-        <v>49794</v>
+        <v>18216</v>
       </c>
       <c r="Q199" t="n">
-        <v>96.3</v>
+        <v>107.8</v>
       </c>
     </row>
     <row r="200">
@@ -13444,31 +13444,31 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>640</v>
+        <v>316</v>
       </c>
       <c r="J200" t="n">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="K200" t="n">
-        <v>578</v>
+        <v>284</v>
       </c>
       <c r="L200" t="n">
-        <v>123</v>
+        <v>45</v>
       </c>
       <c r="M200" t="n">
-        <v>90.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N200" t="n">
-        <v>100.8</v>
+        <v>112.5</v>
       </c>
       <c r="O200" t="n">
-        <v>64640</v>
+        <v>29072</v>
       </c>
       <c r="P200" t="n">
-        <v>58378</v>
+        <v>26128</v>
       </c>
       <c r="Q200" t="n">
-        <v>90.3</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -13509,31 +13509,31 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>674</v>
+        <v>408</v>
       </c>
       <c r="J201" t="n">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="K201" t="n">
-        <v>728</v>
+        <v>367</v>
       </c>
       <c r="L201" t="n">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="M201" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="N201" t="n">
-        <v>107.9</v>
+        <v>106.2</v>
       </c>
       <c r="O201" t="n">
-        <v>92338</v>
+        <v>42024</v>
       </c>
       <c r="P201" t="n">
-        <v>99736</v>
+        <v>37801</v>
       </c>
       <c r="Q201" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="202">
@@ -13574,31 +13574,31 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>719</v>
+        <v>229</v>
       </c>
       <c r="J202" t="n">
-        <v>172</v>
+        <v>45</v>
       </c>
       <c r="K202" t="n">
-        <v>726</v>
+        <v>209</v>
       </c>
       <c r="L202" t="n">
-        <v>188</v>
+        <v>51</v>
       </c>
       <c r="M202" t="n">
-        <v>101</v>
+        <v>91.3</v>
       </c>
       <c r="N202" t="n">
-        <v>109.3</v>
+        <v>113.3</v>
       </c>
       <c r="O202" t="n">
-        <v>92032</v>
+        <v>21984</v>
       </c>
       <c r="P202" t="n">
-        <v>92928</v>
+        <v>20064</v>
       </c>
       <c r="Q202" t="n">
-        <v>101</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="203">
@@ -13639,31 +13639,31 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>675</v>
+        <v>241</v>
       </c>
       <c r="J203" t="n">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="K203" t="n">
-        <v>657</v>
+        <v>257</v>
       </c>
       <c r="L203" t="n">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="M203" t="n">
-        <v>97.3</v>
+        <v>106.6</v>
       </c>
       <c r="N203" t="n">
-        <v>103.1</v>
+        <v>86.2</v>
       </c>
       <c r="O203" t="n">
-        <v>68850</v>
+        <v>29884</v>
       </c>
       <c r="P203" t="n">
-        <v>67014</v>
+        <v>31868</v>
       </c>
       <c r="Q203" t="n">
-        <v>97.3</v>
+        <v>106.6</v>
       </c>
     </row>
     <row r="204">
@@ -13704,31 +13704,31 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>612</v>
+        <v>233</v>
       </c>
       <c r="J204" t="n">
-        <v>134</v>
+        <v>45</v>
       </c>
       <c r="K204" t="n">
-        <v>616</v>
+        <v>263</v>
       </c>
       <c r="L204" t="n">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="M204" t="n">
-        <v>100.7</v>
+        <v>112.9</v>
       </c>
       <c r="N204" t="n">
-        <v>106</v>
+        <v>102.2</v>
       </c>
       <c r="O204" t="n">
-        <v>62424</v>
+        <v>25630</v>
       </c>
       <c r="P204" t="n">
-        <v>62832</v>
+        <v>28930</v>
       </c>
       <c r="Q204" t="n">
-        <v>100.7</v>
+        <v>112.9</v>
       </c>
     </row>
     <row r="205">
@@ -13769,31 +13769,31 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>599</v>
+        <v>391</v>
       </c>
       <c r="J205" t="n">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="K205" t="n">
-        <v>658</v>
+        <v>369</v>
       </c>
       <c r="L205" t="n">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="M205" t="n">
-        <v>109.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N205" t="n">
-        <v>100</v>
+        <v>113.7</v>
       </c>
       <c r="O205" t="n">
-        <v>40133</v>
+        <v>24242</v>
       </c>
       <c r="P205" t="n">
-        <v>44086</v>
+        <v>22878</v>
       </c>
       <c r="Q205" t="n">
-        <v>109.8</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -13834,31 +13834,31 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>592</v>
+        <v>447</v>
       </c>
       <c r="J206" t="n">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="K206" t="n">
-        <v>609</v>
+        <v>435</v>
       </c>
       <c r="L206" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="M206" t="n">
-        <v>102.9</v>
+        <v>97.3</v>
       </c>
       <c r="N206" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="O206" t="n">
-        <v>63344</v>
+        <v>54534</v>
       </c>
       <c r="P206" t="n">
-        <v>65163</v>
+        <v>53070</v>
       </c>
       <c r="Q206" t="n">
-        <v>102.9</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="207">
@@ -13899,31 +13899,31 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>516</v>
+        <v>466</v>
       </c>
       <c r="J207" t="n">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="K207" t="n">
-        <v>585</v>
+        <v>399</v>
       </c>
       <c r="L207" t="n">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="M207" t="n">
-        <v>113.4</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="N207" t="n">
-        <v>99</v>
+        <v>112.7</v>
       </c>
       <c r="O207" t="n">
-        <v>67596</v>
+        <v>50794</v>
       </c>
       <c r="P207" t="n">
-        <v>76635</v>
+        <v>43491</v>
       </c>
       <c r="Q207" t="n">
-        <v>113.4</v>
+        <v>85.59999999999999</v>
       </c>
     </row>
     <row r="208">
@@ -13964,31 +13964,31 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>515</v>
+        <v>323</v>
       </c>
       <c r="J208" t="n">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="K208" t="n">
-        <v>557</v>
+        <v>342</v>
       </c>
       <c r="L208" t="n">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="M208" t="n">
-        <v>108.2</v>
+        <v>105.9</v>
       </c>
       <c r="N208" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O208" t="n">
-        <v>52015</v>
+        <v>23902</v>
       </c>
       <c r="P208" t="n">
-        <v>56257</v>
+        <v>25308</v>
       </c>
       <c r="Q208" t="n">
-        <v>108.2</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="209">
@@ -14029,31 +14029,31 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>536</v>
+        <v>331</v>
       </c>
       <c r="J209" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="K209" t="n">
-        <v>606</v>
+        <v>300</v>
       </c>
       <c r="L209" t="n">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="M209" t="n">
-        <v>113.1</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="N209" t="n">
-        <v>107.2</v>
+        <v>112.5</v>
       </c>
       <c r="O209" t="n">
-        <v>31088</v>
+        <v>35417</v>
       </c>
       <c r="P209" t="n">
-        <v>35148</v>
+        <v>32100</v>
       </c>
       <c r="Q209" t="n">
-        <v>113.1</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="210">
@@ -14094,31 +14094,31 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>534</v>
+        <v>175</v>
       </c>
       <c r="J210" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="K210" t="n">
-        <v>540</v>
+        <v>188</v>
       </c>
       <c r="L210" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="M210" t="n">
-        <v>101.1</v>
+        <v>107.4</v>
       </c>
       <c r="N210" t="n">
-        <v>101.1</v>
+        <v>110.9</v>
       </c>
       <c r="O210" t="n">
-        <v>31506</v>
+        <v>13300</v>
       </c>
       <c r="P210" t="n">
-        <v>31860</v>
+        <v>14288</v>
       </c>
       <c r="Q210" t="n">
-        <v>101.1</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="211">
@@ -14159,31 +14159,31 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>684</v>
+        <v>206</v>
       </c>
       <c r="J211" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="K211" t="n">
-        <v>690</v>
+        <v>198</v>
       </c>
       <c r="L211" t="n">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="M211" t="n">
-        <v>100.9</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N211" t="n">
-        <v>107.4</v>
+        <v>103.1</v>
       </c>
       <c r="O211" t="n">
-        <v>34200</v>
+        <v>11330</v>
       </c>
       <c r="P211" t="n">
-        <v>34500</v>
+        <v>10890</v>
       </c>
       <c r="Q211" t="n">
-        <v>100.9</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="212">
@@ -14224,31 +14224,31 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>545</v>
+        <v>350</v>
       </c>
       <c r="J212" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="K212" t="n">
-        <v>606</v>
+        <v>318</v>
       </c>
       <c r="L212" t="n">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="M212" t="n">
-        <v>111.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N212" t="n">
-        <v>106.2</v>
+        <v>98.2</v>
       </c>
       <c r="O212" t="n">
-        <v>77390</v>
+        <v>20650</v>
       </c>
       <c r="P212" t="n">
-        <v>86052</v>
+        <v>18762</v>
       </c>
       <c r="Q212" t="n">
-        <v>111.2</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="213">
@@ -14289,31 +14289,31 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>626</v>
+        <v>271</v>
       </c>
       <c r="J213" t="n">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="K213" t="n">
-        <v>585</v>
+        <v>252</v>
       </c>
       <c r="L213" t="n">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="M213" t="n">
-        <v>93.5</v>
+        <v>93</v>
       </c>
       <c r="N213" t="n">
-        <v>110.3</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="O213" t="n">
-        <v>70738</v>
+        <v>19783</v>
       </c>
       <c r="P213" t="n">
-        <v>66105</v>
+        <v>18396</v>
       </c>
       <c r="Q213" t="n">
-        <v>93.5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="214">
@@ -14354,31 +14354,31 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>516</v>
+        <v>245</v>
       </c>
       <c r="J214" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="K214" t="n">
-        <v>460</v>
+        <v>268</v>
       </c>
       <c r="L214" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="M214" t="n">
-        <v>89.09999999999999</v>
+        <v>109.4</v>
       </c>
       <c r="N214" t="n">
-        <v>103.6</v>
+        <v>90.2</v>
       </c>
       <c r="O214" t="n">
-        <v>28896</v>
+        <v>20090</v>
       </c>
       <c r="P214" t="n">
-        <v>25760</v>
+        <v>21976</v>
       </c>
       <c r="Q214" t="n">
-        <v>89.09999999999999</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="215">
@@ -14419,31 +14419,31 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>458</v>
+        <v>229</v>
       </c>
       <c r="J215" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="K215" t="n">
-        <v>466</v>
+        <v>235</v>
       </c>
       <c r="L215" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="M215" t="n">
-        <v>101.7</v>
+        <v>102.6</v>
       </c>
       <c r="N215" t="n">
-        <v>100</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O215" t="n">
-        <v>26106</v>
+        <v>34121</v>
       </c>
       <c r="P215" t="n">
-        <v>26562</v>
+        <v>35015</v>
       </c>
       <c r="Q215" t="n">
-        <v>101.7</v>
+        <v>102.6</v>
       </c>
     </row>
     <row r="216">
@@ -14484,31 +14484,31 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>491</v>
+        <v>260</v>
       </c>
       <c r="J216" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="K216" t="n">
-        <v>495</v>
+        <v>270</v>
       </c>
       <c r="L216" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="M216" t="n">
-        <v>100.8</v>
+        <v>103.8</v>
       </c>
       <c r="N216" t="n">
-        <v>107.4</v>
+        <v>100</v>
       </c>
       <c r="O216" t="n">
-        <v>43208</v>
+        <v>16640</v>
       </c>
       <c r="P216" t="n">
-        <v>43560</v>
+        <v>17280</v>
       </c>
       <c r="Q216" t="n">
-        <v>100.8</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="217">
@@ -14549,31 +14549,31 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>445</v>
+        <v>329</v>
       </c>
       <c r="J217" t="n">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="K217" t="n">
-        <v>494</v>
+        <v>279</v>
       </c>
       <c r="L217" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="M217" t="n">
-        <v>111</v>
+        <v>84.8</v>
       </c>
       <c r="N217" t="n">
-        <v>105.6</v>
+        <v>109.8</v>
       </c>
       <c r="O217" t="n">
-        <v>40495</v>
+        <v>23359</v>
       </c>
       <c r="P217" t="n">
-        <v>44954</v>
+        <v>19809</v>
       </c>
       <c r="Q217" t="n">
-        <v>111</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="218">
@@ -14614,31 +14614,31 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>285</v>
+        <v>527</v>
       </c>
       <c r="J218" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K218" t="n">
-        <v>294</v>
+        <v>505</v>
       </c>
       <c r="L218" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="M218" t="n">
-        <v>103.2</v>
+        <v>95.8</v>
       </c>
       <c r="N218" t="n">
-        <v>95.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="O218" t="n">
-        <v>16245</v>
+        <v>30566</v>
       </c>
       <c r="P218" t="n">
-        <v>16758</v>
+        <v>29290</v>
       </c>
       <c r="Q218" t="n">
-        <v>103.2</v>
+        <v>95.8</v>
       </c>
     </row>
     <row r="219">
@@ -14679,31 +14679,31 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>348</v>
+        <v>457</v>
       </c>
       <c r="J219" t="n">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="K219" t="n">
-        <v>319</v>
+        <v>448</v>
       </c>
       <c r="L219" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="M219" t="n">
-        <v>91.7</v>
+        <v>98</v>
       </c>
       <c r="N219" t="n">
-        <v>85.7</v>
+        <v>114.3</v>
       </c>
       <c r="O219" t="n">
-        <v>49764</v>
+        <v>37474</v>
       </c>
       <c r="P219" t="n">
-        <v>45617</v>
+        <v>36736</v>
       </c>
       <c r="Q219" t="n">
-        <v>91.7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="220">
@@ -14744,31 +14744,31 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>361</v>
+        <v>171</v>
       </c>
       <c r="J220" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="K220" t="n">
-        <v>328</v>
+        <v>176</v>
       </c>
       <c r="L220" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M220" t="n">
-        <v>90.90000000000001</v>
+        <v>102.9</v>
       </c>
       <c r="N220" t="n">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="O220" t="n">
-        <v>49457</v>
+        <v>11628</v>
       </c>
       <c r="P220" t="n">
-        <v>44936</v>
+        <v>11968</v>
       </c>
       <c r="Q220" t="n">
-        <v>90.90000000000001</v>
+        <v>102.9</v>
       </c>
     </row>
     <row r="221">
@@ -14809,31 +14809,31 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>534</v>
+        <v>222</v>
       </c>
       <c r="J221" t="n">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="K221" t="n">
-        <v>476</v>
+        <v>197</v>
       </c>
       <c r="L221" t="n">
-        <v>97</v>
+        <v>33</v>
       </c>
       <c r="M221" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="N221" t="n">
-        <v>92.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="O221" t="n">
-        <v>58206</v>
+        <v>19314</v>
       </c>
       <c r="P221" t="n">
-        <v>51884</v>
+        <v>17139</v>
       </c>
       <c r="Q221" t="n">
-        <v>89.09999999999999</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="222">
@@ -14874,31 +14874,31 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="J222" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="K222" t="n">
-        <v>184</v>
+        <v>225</v>
       </c>
       <c r="L222" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="M222" t="n">
-        <v>94.8</v>
+        <v>88.2</v>
       </c>
       <c r="N222" t="n">
-        <v>103.8</v>
+        <v>86.3</v>
       </c>
       <c r="O222" t="n">
-        <v>20952</v>
+        <v>16830</v>
       </c>
       <c r="P222" t="n">
-        <v>19872</v>
+        <v>14850</v>
       </c>
       <c r="Q222" t="n">
-        <v>94.8</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="223">
@@ -14939,31 +14939,31 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>216</v>
+        <v>182</v>
       </c>
       <c r="J223" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K223" t="n">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="L223" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="M223" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="N223" t="n">
         <v>109.3</v>
       </c>
-      <c r="N223" t="n">
-        <v>86.8</v>
-      </c>
       <c r="O223" t="n">
-        <v>12960</v>
+        <v>24024</v>
       </c>
       <c r="P223" t="n">
-        <v>14160</v>
+        <v>25740</v>
       </c>
       <c r="Q223" t="n">
-        <v>109.3</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="224">
@@ -15004,31 +15004,31 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>237</v>
+        <v>140</v>
       </c>
       <c r="J224" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K224" t="n">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="L224" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="M224" t="n">
-        <v>90.3</v>
+        <v>100.7</v>
       </c>
       <c r="N224" t="n">
-        <v>87.5</v>
+        <v>110</v>
       </c>
       <c r="O224" t="n">
-        <v>31047</v>
+        <v>10220</v>
       </c>
       <c r="P224" t="n">
-        <v>28034</v>
+        <v>10293</v>
       </c>
       <c r="Q224" t="n">
-        <v>90.3</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="225">
@@ -15069,31 +15069,31 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>178</v>
+        <v>115</v>
       </c>
       <c r="J225" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K225" t="n">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="L225" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="M225" t="n">
-        <v>95.5</v>
+        <v>106.1</v>
       </c>
       <c r="N225" t="n">
-        <v>103.2</v>
+        <v>95.7</v>
       </c>
       <c r="O225" t="n">
-        <v>25810</v>
+        <v>16790</v>
       </c>
       <c r="P225" t="n">
-        <v>24650</v>
+        <v>17812</v>
       </c>
       <c r="Q225" t="n">
-        <v>95.5</v>
+        <v>106.1</v>
       </c>
     </row>
     <row r="226">
@@ -15134,31 +15134,31 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="J226" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="K226" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="L226" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="M226" t="n">
-        <v>86.2</v>
+        <v>111</v>
       </c>
       <c r="N226" t="n">
-        <v>88.2</v>
+        <v>87</v>
       </c>
       <c r="O226" t="n">
-        <v>24947</v>
+        <v>28215</v>
       </c>
       <c r="P226" t="n">
-        <v>21513</v>
+        <v>31320</v>
       </c>
       <c r="Q226" t="n">
-        <v>86.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="227">
@@ -15199,31 +15199,31 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="J227" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="K227" t="n">
-        <v>273</v>
+        <v>238</v>
       </c>
       <c r="L227" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="M227" t="n">
-        <v>95.09999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="N227" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="O227" t="n">
-        <v>28413</v>
+        <v>23229</v>
       </c>
       <c r="P227" t="n">
-        <v>27027</v>
+        <v>21182</v>
       </c>
       <c r="Q227" t="n">
-        <v>95.09999999999999</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="228">
@@ -15264,31 +15264,31 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>281</v>
+        <v>360</v>
       </c>
       <c r="J228" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="K228" t="n">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="L228" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="M228" t="n">
-        <v>87.5</v>
+        <v>90.8</v>
       </c>
       <c r="N228" t="n">
-        <v>96.7</v>
+        <v>98.8</v>
       </c>
       <c r="O228" t="n">
-        <v>20794</v>
+        <v>39600</v>
       </c>
       <c r="P228" t="n">
-        <v>18204</v>
+        <v>35970</v>
       </c>
       <c r="Q228" t="n">
-        <v>87.5</v>
+        <v>90.8</v>
       </c>
     </row>
     <row r="229">
@@ -15329,31 +15329,31 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="J229" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="K229" t="n">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="L229" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="M229" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="N229" t="n">
-        <v>91.8</v>
+        <v>102.1</v>
       </c>
       <c r="O229" t="n">
-        <v>48477</v>
+        <v>20748</v>
       </c>
       <c r="P229" t="n">
-        <v>42375</v>
+        <v>18148</v>
       </c>
       <c r="Q229" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="230">
@@ -15394,31 +15394,31 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>225</v>
+        <v>370</v>
       </c>
       <c r="J230" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K230" t="n">
-        <v>235</v>
+        <v>393</v>
       </c>
       <c r="L230" t="n">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="M230" t="n">
-        <v>104.4</v>
+        <v>106.2</v>
       </c>
       <c r="N230" t="n">
-        <v>94</v>
+        <v>107.1</v>
       </c>
       <c r="O230" t="n">
-        <v>24300</v>
+        <v>48840</v>
       </c>
       <c r="P230" t="n">
-        <v>25380</v>
+        <v>51876</v>
       </c>
       <c r="Q230" t="n">
-        <v>104.4</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="231">
@@ -15459,31 +15459,31 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>470</v>
+        <v>435</v>
       </c>
       <c r="J231" t="n">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="K231" t="n">
-        <v>471</v>
+        <v>408</v>
       </c>
       <c r="L231" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M231" t="n">
-        <v>100.2</v>
+        <v>93.8</v>
       </c>
       <c r="N231" t="n">
-        <v>86.40000000000001</v>
+        <v>103.3</v>
       </c>
       <c r="O231" t="n">
-        <v>45590</v>
+        <v>33930</v>
       </c>
       <c r="P231" t="n">
-        <v>45687</v>
+        <v>31824</v>
       </c>
       <c r="Q231" t="n">
-        <v>100.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="232">
@@ -15527,28 +15527,28 @@
         <v>334</v>
       </c>
       <c r="J232" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="K232" t="n">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="L232" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M232" t="n">
-        <v>92.2</v>
+        <v>86.5</v>
       </c>
       <c r="N232" t="n">
-        <v>113.6</v>
+        <v>98.2</v>
       </c>
       <c r="O232" t="n">
-        <v>24382</v>
+        <v>20040</v>
       </c>
       <c r="P232" t="n">
-        <v>22484</v>
+        <v>17340</v>
       </c>
       <c r="Q232" t="n">
-        <v>92.2</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="233">
@@ -15589,31 +15589,31 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>477</v>
+        <v>374</v>
       </c>
       <c r="J233" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="K233" t="n">
-        <v>408</v>
+        <v>348</v>
       </c>
       <c r="L233" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="M233" t="n">
-        <v>85.5</v>
+        <v>93</v>
       </c>
       <c r="N233" t="n">
-        <v>85.2</v>
+        <v>95.3</v>
       </c>
       <c r="O233" t="n">
-        <v>65826</v>
+        <v>32912</v>
       </c>
       <c r="P233" t="n">
-        <v>56304</v>
+        <v>30624</v>
       </c>
       <c r="Q233" t="n">
-        <v>85.5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="234">
@@ -15654,31 +15654,31 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>301</v>
+        <v>192</v>
       </c>
       <c r="J234" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="K234" t="n">
-        <v>295</v>
+        <v>176</v>
       </c>
       <c r="L234" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="M234" t="n">
-        <v>98</v>
+        <v>91.7</v>
       </c>
       <c r="N234" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="O234" t="n">
-        <v>43043</v>
+        <v>26112</v>
       </c>
       <c r="P234" t="n">
-        <v>42185</v>
+        <v>23936</v>
       </c>
       <c r="Q234" t="n">
-        <v>98</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="235">
@@ -15719,31 +15719,31 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="J235" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="K235" t="n">
-        <v>275</v>
+        <v>149</v>
       </c>
       <c r="L235" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="M235" t="n">
-        <v>110.4</v>
+        <v>108.8</v>
       </c>
       <c r="N235" t="n">
-        <v>104.6</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="O235" t="n">
-        <v>12450</v>
+        <v>18906</v>
       </c>
       <c r="P235" t="n">
-        <v>13750</v>
+        <v>20562</v>
       </c>
       <c r="Q235" t="n">
-        <v>110.4</v>
+        <v>108.8</v>
       </c>
     </row>
     <row r="236">
@@ -15784,31 +15784,31 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="J236" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K236" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="L236" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="M236" t="n">
-        <v>89.2</v>
+        <v>101.5</v>
       </c>
       <c r="N236" t="n">
-        <v>110.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="O236" t="n">
-        <v>16279</v>
+        <v>12416</v>
       </c>
       <c r="P236" t="n">
-        <v>14527</v>
+        <v>12608</v>
       </c>
       <c r="Q236" t="n">
-        <v>89.2</v>
+        <v>101.5</v>
       </c>
     </row>
     <row r="237">
@@ -15849,31 +15849,31 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="J237" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="K237" t="n">
-        <v>255</v>
+        <v>302</v>
       </c>
       <c r="L237" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M237" t="n">
-        <v>108.1</v>
+        <v>100.7</v>
       </c>
       <c r="N237" t="n">
-        <v>95.8</v>
+        <v>110</v>
       </c>
       <c r="O237" t="n">
-        <v>24780</v>
+        <v>18900</v>
       </c>
       <c r="P237" t="n">
-        <v>26775</v>
+        <v>19026</v>
       </c>
       <c r="Q237" t="n">
-        <v>108.1</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="238">
@@ -15914,31 +15914,31 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="J238" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K238" t="n">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="L238" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="M238" t="n">
-        <v>97.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="N238" t="n">
-        <v>110</v>
+        <v>109.8</v>
       </c>
       <c r="O238" t="n">
-        <v>11832</v>
+        <v>28674</v>
       </c>
       <c r="P238" t="n">
-        <v>11560</v>
+        <v>27258</v>
       </c>
       <c r="Q238" t="n">
-        <v>97.7</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="239">
@@ -15979,31 +15979,31 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>192</v>
+        <v>316</v>
       </c>
       <c r="J239" t="n">
+        <v>40</v>
+      </c>
+      <c r="K239" t="n">
+        <v>300</v>
+      </c>
+      <c r="L239" t="n">
         <v>36</v>
       </c>
-      <c r="K239" t="n">
-        <v>177</v>
-      </c>
-      <c r="L239" t="n">
-        <v>34</v>
-      </c>
       <c r="M239" t="n">
-        <v>92.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="N239" t="n">
-        <v>94.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="O239" t="n">
-        <v>21312</v>
+        <v>22436</v>
       </c>
       <c r="P239" t="n">
-        <v>19647</v>
+        <v>21300</v>
       </c>
       <c r="Q239" t="n">
-        <v>92.2</v>
+        <v>94.90000000000001</v>
       </c>
     </row>
     <row r="240">
@@ -16044,31 +16044,31 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>153</v>
+        <v>446</v>
       </c>
       <c r="J240" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="K240" t="n">
-        <v>163</v>
+        <v>398</v>
       </c>
       <c r="L240" t="n">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="M240" t="n">
-        <v>106.5</v>
+        <v>89.2</v>
       </c>
       <c r="N240" t="n">
-        <v>93</v>
+        <v>97.3</v>
       </c>
       <c r="O240" t="n">
-        <v>11628</v>
+        <v>45046</v>
       </c>
       <c r="P240" t="n">
-        <v>12388</v>
+        <v>40198</v>
       </c>
       <c r="Q240" t="n">
-        <v>106.5</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="241">
@@ -16109,31 +16109,31 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>250</v>
+        <v>532</v>
       </c>
       <c r="J241" t="n">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="K241" t="n">
-        <v>239</v>
+        <v>452</v>
       </c>
       <c r="L241" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="M241" t="n">
-        <v>95.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="N241" t="n">
-        <v>88.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="O241" t="n">
-        <v>21750</v>
+        <v>76076</v>
       </c>
       <c r="P241" t="n">
-        <v>20793</v>
+        <v>64636</v>
       </c>
       <c r="Q241" t="n">
-        <v>95.59999999999999</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
